--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2704D0-8434-E045-A273-8352660C57B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F5BCA-2AEF-FE49-81CC-9569A046230A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jobs" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="510">
   <si>
     <t>title</t>
   </si>
@@ -56,13 +56,1513 @@
   </si>
   <si>
     <t>score</t>
+  </si>
+  <si>
+    <t>JOB-000100</t>
+  </si>
+  <si>
+    <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
+  </si>
+  <si>
+    <t>MR applications, interactive content</t>
+  </si>
+  <si>
+    <t>MR programmers develop interactive and immersive experiences using both virtual and augmented reality, blending the real and virtual worlds.</t>
+  </si>
+  <si>
+    <t>Mixed Reality (MR) Programmer</t>
+  </si>
+  <si>
+    <t>JOB-000099</t>
+  </si>
+  <si>
+    <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
+  </si>
+  <si>
+    <t>BI reports, data analytics platforms</t>
+  </si>
+  <si>
+    <t>MicroStrategy developers design and implement business intelligence solutions using the MicroStrategy platform, focusing on reporting and data analysis.</t>
+  </si>
+  <si>
+    <t>MicroStrategy Developer</t>
+  </si>
+  <si>
+    <t>JOB-000098</t>
+  </si>
+  <si>
+    <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
+  </si>
+  <si>
+    <t>Machine learning models, data-driven insights</t>
+  </si>
+  <si>
+    <t>Machine learning engineers develop algorithms that allow systems to improve over time based on data, working with large datasets to build predictive models.</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000097</t>
+  </si>
+  <si>
+    <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
+  </si>
+  <si>
+    <t>Hardware setup, software installation</t>
+  </si>
+  <si>
+    <t>IT technicians install, configure, and maintain hardware and software systems, assisting users and ensuring smooth operation of company devices and systems.</t>
+  </si>
+  <si>
+    <t>IT Technician</t>
+  </si>
+  <si>
+    <t>JOB-000096</t>
+  </si>
+  <si>
+    <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
+  </si>
+  <si>
+    <t>Technical support tickets, system maintenance</t>
+  </si>
+  <si>
+    <t>IT support specialists provide technical assistance for users, troubleshooting hardware/software issues and maintaining systems and networks.</t>
+  </si>
+  <si>
+    <t>IT Support Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000095</t>
+  </si>
+  <si>
+    <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
+  </si>
+  <si>
+    <t>IoT solutions, connected devices</t>
+  </si>
+  <si>
+    <t>IoT specialists design and manage interconnected systems and devices, ensuring secure data transfer and real-time functionality for the Internet of Things.</t>
+  </si>
+  <si>
+    <t>IoT Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000094</t>
+  </si>
+  <si>
+    <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
+  </si>
+  <si>
+    <t>iOS apps, mobile solutions</t>
+  </si>
+  <si>
+    <t>iOS developers create applications for Apple's ecosystem, ensuring a seamless user experience across iPhones, iPads, and other Apple devices.</t>
+  </si>
+  <si>
+    <t>iOS Developer</t>
+  </si>
+  <si>
+    <t>JOB-000093</t>
+  </si>
+  <si>
+    <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
+  </si>
+  <si>
+    <t>IT infrastructure, architecture plans</t>
+  </si>
+  <si>
+    <t>Infrastructure architects design and manage the underlying IT infrastructure, ensuring that systems are scalable, secure, and reliable to support business operations.</t>
+  </si>
+  <si>
+    <t>Infrastructure Architect</t>
+  </si>
+  <si>
+    <t>JOB-000092</t>
+  </si>
+  <si>
+    <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
+  </si>
+  <si>
+    <t>Security policies, compliance reports</t>
+  </si>
+  <si>
+    <t>Information security officers develop and enforce policies to protect sensitive data and networks from internal and external threats.</t>
+  </si>
+  <si>
+    <t>Information Security Officer</t>
+  </si>
+  <si>
+    <t>JOB-000091</t>
+  </si>
+  <si>
+    <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
+  </si>
+  <si>
+    <t>Security protocols, vulnerability reports</t>
+  </si>
+  <si>
+    <t>Information security analysts assess and secure an organization's IT infrastructure by identifying vulnerabilities, monitoring systems, and responding to incidents.</t>
+  </si>
+  <si>
+    <t>Information Security Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000090</t>
+  </si>
+  <si>
+    <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
+  </si>
+  <si>
+    <t>ETL processes, data integrations</t>
+  </si>
+  <si>
+    <t>Informatica developers design and implement data integration solutions using Informatica tools to facilitate data movement and transformation across platforms.</t>
+  </si>
+  <si>
+    <t>Informatica Developer</t>
+  </si>
+  <si>
+    <t>JOB-000089</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
+  </si>
+  <si>
+    <t>Full web applications, APIs, services</t>
+  </si>
+  <si>
+    <t>Full-stack developers handle both the front-end and back-end of web applications, ensuring smooth communication between the user interface and databases.</t>
+  </si>
+  <si>
+    <t>Full-Stack Developer</t>
+  </si>
+  <si>
+    <t>JOB-000088</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
+  </si>
+  <si>
+    <t>Websites, user interfaces, web apps</t>
+  </si>
+  <si>
+    <t>Front-end developers design and build the user-facing components of websites and applications, ensuring responsive design and user experience.</t>
+  </si>
+  <si>
+    <t>Front-End Developer</t>
+  </si>
+  <si>
+    <t>JOB-000087</t>
+  </si>
+  <si>
+    <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
+  </si>
+  <si>
+    <t>XR applications, immersive experiences</t>
+  </si>
+  <si>
+    <t>XR programmers create immersive experiences using augmented reality (AR), virtual reality (VR), and mixed reality (MR), developing applications for various industries.</t>
+  </si>
+  <si>
+    <t>Extended Reality (XR) Programmer</t>
+  </si>
+  <si>
+    <t>JOB-000086</t>
+  </si>
+  <si>
+    <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
+  </si>
+  <si>
+    <t>ETL pipelines, data transformations</t>
+  </si>
+  <si>
+    <t>ETL (Extract, Transform, Load) developers design and manage data workflows to extract data from various sources, transform it into a usable format, and load it into databases.</t>
+  </si>
+  <si>
+    <t>ETL Developer</t>
+  </si>
+  <si>
+    <t>JOB-000085</t>
+  </si>
+  <si>
+    <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
+  </si>
+  <si>
+    <t>Continuous integration pipelines, deployment automation</t>
+  </si>
+  <si>
+    <t>DevOps engineers automate and streamline the deployment, integration, and monitoring of applications and infrastructure, ensuring faster development cycles.</t>
+  </si>
+  <si>
+    <t>DevOps Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000084</t>
+  </si>
+  <si>
+    <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
+  </si>
+  <si>
+    <t>Resolved technical issues, support tickets</t>
+  </si>
+  <si>
+    <t>Desktop support technicians troubleshoot and resolve hardware and software issues on desktops and laptops, providing technical support to end users.</t>
+  </si>
+  <si>
+    <t>Desktop Support Technician</t>
+  </si>
+  <si>
+    <t>JOB-000083</t>
+  </si>
+  <si>
+    <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
+  </si>
+  <si>
+    <t>Deep learning models, AI applications</t>
+  </si>
+  <si>
+    <t>Deep learning specialists focus on advanced machine learning techniques, creating neural networks and AI models for tasks like image recognition and natural language processing.</t>
+  </si>
+  <si>
+    <t>Deep Learning Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000082</t>
+  </si>
+  <si>
+    <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
+  </si>
+  <si>
+    <t>Data warehouses, ETL pipelines</t>
+  </si>
+  <si>
+    <t>Data warehouse specialists design, implement, and manage large-scale data storage systems, ensuring that data is organized, accessible, and optimized for analysis.</t>
+  </si>
+  <si>
+    <t>Datawarehouse Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000081</t>
+  </si>
+  <si>
+    <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
+  </si>
+  <si>
+    <t>Test reports, database issues</t>
+  </si>
+  <si>
+    <t>Database testers validate and test databases to ensure data accuracy, integrity, and functionality by executing test cases and identifying bugs.</t>
+  </si>
+  <si>
+    <t>Database Tester</t>
+  </si>
+  <si>
+    <t>JOB-000080</t>
+  </si>
+  <si>
+    <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
+  </si>
+  <si>
+    <t>Database maintenance, troubleshooting</t>
+  </si>
+  <si>
+    <t>Database support specialists provide technical support for database systems, troubleshooting issues and ensuring smooth operations.</t>
+  </si>
+  <si>
+    <t>Database Support Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000079</t>
+  </si>
+  <si>
+    <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
+  </si>
+  <si>
+    <t>Database performance, backups, security</t>
+  </si>
+  <si>
+    <t>DBAs manage and maintain databases, ensuring their performance, integrity, and security while troubleshooting and resolving issues.</t>
+  </si>
+  <si>
+    <t>Database Administrator (DBA)</t>
+  </si>
+  <si>
+    <t>JOB-000078</t>
+  </si>
+  <si>
+    <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
+  </si>
+  <si>
+    <t>Predictive models, machine learning algorithms</t>
+  </si>
+  <si>
+    <t>Data scientists analyze complex data sets using advanced statistical, mathematical, and programming techniques to build models and predictions.</t>
+  </si>
+  <si>
+    <t>Data Scientist</t>
+  </si>
+  <si>
+    <t>JOB-000077</t>
+  </si>
+  <si>
+    <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
+  </si>
+  <si>
+    <t>Data models, data structures</t>
+  </si>
+  <si>
+    <t>Data modelers design data models, structures, and databases, ensuring that data is stored efficiently and can be easily accessed for analysis.</t>
+  </si>
+  <si>
+    <t>Data Modeler</t>
+  </si>
+  <si>
+    <t>JOB-000076</t>
+  </si>
+  <si>
+    <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
+  </si>
+  <si>
+    <t>Data pipelines, data storage systems</t>
+  </si>
+  <si>
+    <t>Data engineers design, build, and maintain data pipelines and infrastructure, ensuring smooth flow and storage of data for analysis.</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000075</t>
+  </si>
+  <si>
+    <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
+  </si>
+  <si>
+    <t>Data center infrastructure, network systems</t>
+  </si>
+  <si>
+    <t>Data center engineers manage and maintain the physical and virtual infrastructure of data centers, ensuring high availability, performance, and security.</t>
+  </si>
+  <si>
+    <t>Data Center Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000074</t>
+  </si>
+  <si>
+    <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
+  </si>
+  <si>
+    <t>Data architecture, data models</t>
+  </si>
+  <si>
+    <t>Data architects design and structure data systems, ensuring that data is accessible, secure, and scalable across various platforms and applications.</t>
+  </si>
+  <si>
+    <t>Data Architect</t>
+  </si>
+  <si>
+    <t>JOB-000073</t>
+  </si>
+  <si>
+    <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
+  </si>
+  <si>
+    <t>Analytics reports, recommendations</t>
+  </si>
+  <si>
+    <t>Data analytics consultants help organizations optimize their data strategy, analyzing business data to provide actionable insights for growth.</t>
+  </si>
+  <si>
+    <t>Data Analytics Consultant</t>
+  </si>
+  <si>
+    <t>JOB-000072</t>
+  </si>
+  <si>
+    <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
+  </si>
+  <si>
+    <t>Data reports, data visualizations</t>
+  </si>
+  <si>
+    <t>Data analysts interpret complex data to help organizations make data-driven decisions, often working with raw data and presenting findings to stakeholders.</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000071</t>
+  </si>
+  <si>
+    <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
+  </si>
+  <si>
+    <t>Cybersecurity analysts protect an organization's systems and data from cyber threats by monitoring for security breaches, vulnerabilities, and attacks.</t>
+  </si>
+  <si>
+    <t>Cybersecurity Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000070</t>
+  </si>
+  <si>
+    <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
+  </si>
+  <si>
+    <t>Multi-platform apps, mobile/web solutions</t>
+  </si>
+  <si>
+    <t>Cross-platform developers build applications that run seamlessly on multiple operating systems, reducing development time and cost.</t>
+  </si>
+  <si>
+    <t>Cross-Platform Developer</t>
+  </si>
+  <si>
+    <t>JOB-000069</t>
+  </si>
+  <si>
+    <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
+  </si>
+  <si>
+    <t>Cloud infrastructure, cloud services</t>
+  </si>
+  <si>
+    <t>Cloud engineers design, implement, and maintain cloud-based solutions, ensuring scalability, security, and performance across cloud environments.</t>
+  </si>
+  <si>
+    <t>Cloud Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000068</t>
+  </si>
+  <si>
+    <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
+  </si>
+  <si>
+    <t>IT strategy, technology roadmaps</t>
+  </si>
+  <si>
+    <t>The CIO oversees the IT strategy and operations of an organization, ensuring technology aligns with business goals and drives innovation.</t>
+  </si>
+  <si>
+    <t>Chief Information Officer (CIO)</t>
+  </si>
+  <si>
+    <t>JOB-000067</t>
+  </si>
+  <si>
+    <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
+  </si>
+  <si>
+    <t>Requirements documents, business solutions</t>
+  </si>
+  <si>
+    <t>Business analysts assess business processes and identify opportunities for improvement, translating business needs into technical solutions.</t>
+  </si>
+  <si>
+    <t>Business Analyst</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JOB-000066</t>
+  </si>
+  <si>
+    <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
+  </si>
+  <si>
+    <t>Reports, dashboards, data analysis</t>
+  </si>
+  <si>
+    <t>Business Objects developers create and manage business intelligence applications, focusing on data integration, reporting, and analytics.</t>
+  </si>
+  <si>
+    <t>Business Objects Developer</t>
+  </si>
+  <si>
+    <t>JOB-000065</t>
+  </si>
+  <si>
+    <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
+  </si>
+  <si>
+    <t>BI systems, reporting solutions</t>
+  </si>
+  <si>
+    <t>BI developers design and implement the infrastructure for data analysis, creating dashboards, reports, and other tools for decision-making.</t>
+  </si>
+  <si>
+    <t>Business Intelligence Developer</t>
+  </si>
+  <si>
+    <t>JOB-000064</t>
+  </si>
+  <si>
+    <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
+  </si>
+  <si>
+    <t>Data reports, business insights</t>
+  </si>
+  <si>
+    <t>BI analysts evaluate and interpret data to provide insights and recommendations that guide business strategy and improve performance.</t>
+  </si>
+  <si>
+    <t>Business Intelligence Analyst</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JOB-000063</t>
+  </si>
+  <si>
+    <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
+  </si>
+  <si>
+    <t>Blockchain apps, decentralized solutions</t>
+  </si>
+  <si>
+    <t>Blockchain developers create decentralized applications and blockchain platforms, focusing on secure transactions and data integrity using distributed ledger technology.</t>
+  </si>
+  <si>
+    <t>Blockchain Developer</t>
+  </si>
+  <si>
+    <t>JOB-000062</t>
+  </si>
+  <si>
+    <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
+  </si>
+  <si>
+    <t>Big Data platforms, data pipelines</t>
+  </si>
+  <si>
+    <t>Big Data engineers design and manage systems for processing and analyzing large sets of structured and unstructured data across distributed systems.</t>
+  </si>
+  <si>
+    <t>Big Data Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000061</t>
+  </si>
+  <si>
+    <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
+  </si>
+  <si>
+    <t>BI dashboards, reporting tools</t>
+  </si>
+  <si>
+    <t>Business Intelligence (BI) developers design and implement systems that help organizations analyze and interpret data to improve decision-making.</t>
+  </si>
+  <si>
+    <t>BI Developer</t>
+  </si>
+  <si>
+    <t>JOB-000060</t>
+  </si>
+  <si>
+    <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
+  </si>
+  <si>
+    <t>Web services, APIs, server-side systems</t>
+  </si>
+  <si>
+    <t>Back-end developers focus on server-side programming, building and maintaining the infrastructure that supports web applications and databases.</t>
+  </si>
+  <si>
+    <t>Back-End Developer</t>
+  </si>
+  <si>
+    <t>JOB-000059</t>
+  </si>
+  <si>
+    <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
+  </si>
+  <si>
+    <t>AR applications, interactive content</t>
+  </si>
+  <si>
+    <t>AR programmers develop software that overlays digital content onto the real world, enhancing user interactions through augmented reality technology.</t>
+  </si>
+  <si>
+    <t>Augmented Reality (AR) Programmer</t>
+  </si>
+  <si>
+    <t>JOB-000058</t>
+  </si>
+  <si>
+    <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
+  </si>
+  <si>
+    <t>AR/VR apps, immersive experiences</t>
+  </si>
+  <si>
+    <t>AR/VR developers design and implement augmented and virtual reality experiences, creating immersive environments for entertainment, training, and other applications.</t>
+  </si>
+  <si>
+    <t>AR VR Developer</t>
+  </si>
+  <si>
+    <t>JOB-000057</t>
+  </si>
+  <si>
+    <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
+  </si>
+  <si>
+    <t>Android apps, mobile solutions</t>
+  </si>
+  <si>
+    <t>Android developers create mobile applications for Android devices, ensuring seamless user experiences and integration with various device features.</t>
+  </si>
+  <si>
+    <t>Android Developer</t>
+  </si>
+  <si>
+    <t>JOB-000056</t>
+  </si>
+  <si>
+    <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
+  </si>
+  <si>
+    <t>Analytics reports, data insights</t>
+  </si>
+  <si>
+    <t>Analytics managers oversee data analytics teams, guiding them in deriving actionable insights from large datasets to inform business decisions.</t>
+  </si>
+  <si>
+    <t>Analytics Manager</t>
+  </si>
+  <si>
+    <t>JOB-000055</t>
+  </si>
+  <si>
+    <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
+  </si>
+  <si>
+    <t>Research papers, AI algorithms</t>
+  </si>
+  <si>
+    <t>AI research scientists conduct advanced research in artificial intelligence, developing new methodologies and pushing the boundaries of machine learning and AI.</t>
+  </si>
+  <si>
+    <t>AI Research Scientist</t>
+  </si>
+  <si>
+    <t>JOB-000054</t>
+  </si>
+  <si>
+    <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
+  </si>
+  <si>
+    <t>AI models, machine learning algorithms</t>
+  </si>
+  <si>
+    <t>AI programmers design and implement artificial intelligence algorithms and systems, creating intelligent solutions for a range of applications.</t>
+  </si>
+  <si>
+    <t>AI Programmer</t>
+  </si>
+  <si>
+    <t>JOB-000053</t>
+  </si>
+  <si>
+    <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
+  </si>
+  <si>
+    <t>Ethics policies, compliance reports</t>
+  </si>
+  <si>
+    <t>Ethics officers develop and enforce ethical guidelines, ensuring compliance with laws and regulations within an organization.</t>
+  </si>
+  <si>
+    <t>Ethics Officer</t>
+  </si>
+  <si>
+    <t>JOB-000052</t>
+  </si>
+  <si>
+    <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
+  </si>
+  <si>
+    <t>HR strategy reports, talent management plans</t>
+  </si>
+  <si>
+    <t>HR business partners work closely with business leaders to align HR practices with business goals, focusing on workforce planning, development, and strategy.</t>
+  </si>
+  <si>
+    <t>HR Business Partner</t>
+  </si>
+  <si>
+    <t>JOB-000051</t>
+  </si>
+  <si>
+    <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
+  </si>
+  <si>
+    <t>Job offers, candidate databases</t>
+  </si>
+  <si>
+    <t>Recruiters focus on finding and attracting qualified candidates for job openings, guiding them through the hiring process.</t>
+  </si>
+  <si>
+    <t>Recruiter</t>
+  </si>
+  <si>
+    <t>JOB-000050</t>
+  </si>
+  <si>
+    <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
+  </si>
+  <si>
+    <t>Recruitment reports, candidate pipelines</t>
+  </si>
+  <si>
+    <t>HR recruiters source, screen, and hire talent for an organization, managing the recruitment process from job postings to interviews.</t>
+  </si>
+  <si>
+    <t>HR Recruiter</t>
+  </si>
+  <si>
+    <t>JOB-000049</t>
+  </si>
+  <si>
+    <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
+  </si>
+  <si>
+    <t>HR strategy reports, employee programs</t>
+  </si>
+  <si>
+    <t>HR managers oversee HR teams, ensuring the effective management of recruitment, training, employee relations, and performance management.</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>JOB-000048</t>
+  </si>
+  <si>
+    <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
+  </si>
+  <si>
+    <t>Employee records, performance reviews</t>
+  </si>
+  <si>
+    <t>HR generalists handle various HR functions, including recruitment, employee relations, performance management, and policy implementation.</t>
+  </si>
+  <si>
+    <t>HR Generalist</t>
+  </si>
+  <si>
+    <t>JOB-000047</t>
+  </si>
+  <si>
+    <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
+  </si>
+  <si>
+    <t>Compensation reports, benefits strategies</t>
+  </si>
+  <si>
+    <t>Compensation and benefits specialists manage employee pay, benefits packages, and compensation plans, ensuring compliance and competitiveness.</t>
+  </si>
+  <si>
+    <t>Compensation and Benefits Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000046</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
+  </si>
+  <si>
+    <t>Business plans, market analysis reports</t>
+  </si>
+  <si>
+    <t>Business planners develop strategic plans that align company goals with market opportunities, analyzing trends and forecasts.</t>
+  </si>
+  <si>
+    <t>Business Planner</t>
+  </si>
+  <si>
+    <t>JOB-000045</t>
+  </si>
+  <si>
+    <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
+  </si>
+  <si>
+    <t>Research findings, test results</t>
+  </si>
+  <si>
+    <t>Lab technicians conduct scientific experiments, maintain equipment, and analyze data to assist in research and development projects.</t>
+  </si>
+  <si>
+    <t>Lab Technician</t>
+  </si>
+  <si>
+    <t>JOB-000044</t>
+  </si>
+  <si>
+    <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
+  </si>
+  <si>
+    <t>Quality reports, inspection logs</t>
+  </si>
+  <si>
+    <t>Quality control analysts test and inspect products or processes to ensure they meet established standards and regulations.</t>
+  </si>
+  <si>
+    <t>Quality Control Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000043</t>
+  </si>
+  <si>
+    <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
+  </si>
+  <si>
+    <t>Project plans, timelines, budget reports</t>
+  </si>
+  <si>
+    <t>Project managers plan, execute, and close projects, ensuring they are completed on time, within scope, and within budget.</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>JOB-000042</t>
+  </si>
+  <si>
+    <t>Excel, MES software, SAP, Production scheduling tools</t>
+  </si>
+  <si>
+    <t>Production output, quality control reports</t>
+  </si>
+  <si>
+    <t>Production supervisors manage the daily activities of production workers, ensuring product quality and on-time completion.</t>
+  </si>
+  <si>
+    <t>Production Supervisor</t>
+  </si>
+  <si>
+    <t>JOB-000041</t>
+  </si>
+  <si>
+    <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
+  </si>
+  <si>
+    <t>Production schedules, plant safety records</t>
+  </si>
+  <si>
+    <t>Plant managers oversee manufacturing facilities, ensuring efficient production, safety, and compliance with regulations.</t>
+  </si>
+  <si>
+    <t>Plant Manager</t>
+  </si>
+  <si>
+    <t>JOB-000040</t>
+  </si>
+  <si>
+    <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
+  </si>
+  <si>
+    <t>Operational reports, process optimization</t>
+  </si>
+  <si>
+    <t>Operations managers oversee all aspects of daily business activities, optimizing processes to enhance efficiency, reduce costs, and improve performance.</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JOB-000039</t>
+  </si>
+  <si>
+    <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
+  </si>
+  <si>
+    <t>Equipment repair logs, maintenance schedules</t>
+  </si>
+  <si>
+    <t>Maintenance supervisors oversee the maintenance and repair of equipment and facilities, ensuring smooth operational flow.</t>
+  </si>
+  <si>
+    <t>Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>JOB-000038</t>
+  </si>
+  <si>
+    <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
+  </si>
+  <si>
+    <t>Shipping schedules, inventory reports</t>
+  </si>
+  <si>
+    <t>Logistics coordinators manage the supply chain, ensuring the timely and cost-effective transportation and storage of goods.</t>
+  </si>
+  <si>
+    <t>Logistics Coordinator</t>
+  </si>
+  <si>
+    <t>JOB-000037</t>
+  </si>
+  <si>
+    <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
+  </si>
+  <si>
+    <t>Maintenance schedules, facility reports</t>
+  </si>
+  <si>
+    <t>Facilities managers oversee the day-to-day operations of an organization's physical workspace, ensuring maintenance, safety, and efficiency.</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>JOB-000036</t>
+  </si>
+  <si>
+    <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
+  </si>
+  <si>
+    <t>Translated materials, multilingual content</t>
+  </si>
+  <si>
+    <t>Language leads oversee translation projects, manage teams of translators, and ensure quality and accuracy in linguistic services across various languages.</t>
+  </si>
+  <si>
+    <t>Language Lead</t>
+  </si>
+  <si>
+    <t>JOB-000035</t>
+  </si>
+  <si>
+    <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
+  </si>
+  <si>
+    <t>Translated documents, verbal translations</t>
+  </si>
+  <si>
+    <t>Interpreters and translators convert spoken or written content from one language to another, ensuring accuracy and cultural sensitivity.</t>
+  </si>
+  <si>
+    <t>Interpreter-Translator</t>
+  </si>
+  <si>
+    <t>JOB-000034</t>
+  </si>
+  <si>
+    <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
+  </si>
+  <si>
+    <t>Team performance, project results</t>
+  </si>
+  <si>
+    <t>Team leads supervise and guide team members to meet goals, improve productivity, and foster a collaborative work environment.</t>
+  </si>
+  <si>
+    <t>Team Lead</t>
+  </si>
+  <si>
+    <t>JOB-000033</t>
+  </si>
+  <si>
+    <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
+  </si>
+  <si>
+    <t>Optimized production processes, cost savings</t>
+  </si>
+  <si>
+    <t>Process engineers design, implement, and optimize industrial processes in manufacturing and production to ensure efficiency, quality, and cost-effectiveness.</t>
+  </si>
+  <si>
+    <t>Process Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000032</t>
+  </si>
+  <si>
+    <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
+  </si>
+  <si>
+    <t>Product prototypes, mechanical designs</t>
+  </si>
+  <si>
+    <t>Mechanical engineers design, analyze, and manufacture mechanical systems, ensuring functionality and durability in industries like automotive and manufacturing.</t>
+  </si>
+  <si>
+    <t>Mechanical Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000031</t>
+  </si>
+  <si>
+    <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
+  </si>
+  <si>
+    <t>Electrical schematics, system designs</t>
+  </si>
+  <si>
+    <t>Electrical engineers design and test electrical systems and equipment, ensuring efficiency and safety in applications ranging from consumer electronics to power grids.</t>
+  </si>
+  <si>
+    <t>Electrical Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000030</t>
+  </si>
+  <si>
+    <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
+  </si>
+  <si>
+    <t>Construction blueprints, project plans</t>
+  </si>
+  <si>
+    <t>Civil engineers design, plan, and oversee construction projects like roads, bridges, and buildings, ensuring safety, functionality, and environmental impact.</t>
+  </si>
+  <si>
+    <t>Civil Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000029</t>
+  </si>
+  <si>
+    <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
+  </si>
+  <si>
+    <t>Logos, brochures, websites, advertisements</t>
+  </si>
+  <si>
+    <t>Graphic designers create visual content, from logos and websites to marketing materials, ensuring they align with brand identity.</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>JOB-000028</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
+  </si>
+  <si>
+    <t>Office systems, inventory management</t>
+  </si>
+  <si>
+    <t>Office managers supervise office functions, ensure smooth operations, manage supplies, and support administrative teams.</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>JOB-000027</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
+  </si>
+  <si>
+    <t>Office management reports, team coordination</t>
+  </si>
+  <si>
+    <t>The office head oversees office operations, including managing staff, budgets, and overall office efficiency.</t>
+  </si>
+  <si>
+    <t>Office Head</t>
+  </si>
+  <si>
+    <t>JOB-000026</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Google Workspace, Excel, Word</t>
+  </si>
+  <si>
+    <t>Filing systems, office organization</t>
+  </si>
+  <si>
+    <t>Office assistants handle basic administrative tasks such as answering phones, organizing files, and assisting with office operations.</t>
+  </si>
+  <si>
+    <t>Office Assistant</t>
+  </si>
+  <si>
+    <t>JOB-000025</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
+  </si>
+  <si>
+    <t>Calendar schedules, meeting agendas</t>
+  </si>
+  <si>
+    <t>Executive assistants support high-level executives by managing their calendars, arranging meetings, and performing administrative duties.</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>JOB-000024</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
+  </si>
+  <si>
+    <t>Schedules, event planning, reports</t>
+  </si>
+  <si>
+    <t>Administrative coordinators manage daily office tasks, including scheduling, correspondence, and organizing meetings and events.</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>JOB-000023</t>
+  </si>
+  <si>
+    <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
+  </si>
+  <si>
+    <t>Risk models, risk assessments</t>
+  </si>
+  <si>
+    <t>Risk analysts identify, evaluate, and manage financial and operational risks, using quantitative methods to protect an organization's assets.</t>
+  </si>
+  <si>
+    <t>Risk Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000022</t>
+  </si>
+  <si>
+    <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
+  </si>
+  <si>
+    <t>Market analysis reports, property valuations</t>
+  </si>
+  <si>
+    <t>Real estate analysts assess property values, market trends, and investment opportunities, providing data-driven recommendations for investment decisions.</t>
+  </si>
+  <si>
+    <t>Real Estate Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000021</t>
+  </si>
+  <si>
+    <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
+  </si>
+  <si>
+    <t>Compliance audit reports, risk assessments</t>
+  </si>
+  <si>
+    <t>Compliance officers monitor and report on organizational adherence to legal standards, ensuring that financial and operational activities meet regulatory requirements.</t>
+  </si>
+  <si>
+    <t>Compliance Officer</t>
+  </si>
+  <si>
+    <t>JOB-000020</t>
+  </si>
+  <si>
+    <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
+  </si>
+  <si>
+    <t>Compliance reports, policy guidelines</t>
+  </si>
+  <si>
+    <t>Compliance managers develop and enforce policies to ensure an organization adheres to laws, regulations, and internal standards.</t>
+  </si>
+  <si>
+    <t>Compliance Manager</t>
+  </si>
+  <si>
+    <t>JOB-000019</t>
+  </si>
+  <si>
+    <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
+  </si>
+  <si>
+    <t>Audit reports, compliance reviews</t>
+  </si>
+  <si>
+    <t>Internal auditors review and evaluate financial and operational processes to ensure compliance, efficiency, and risk mitigation within an organization.</t>
+  </si>
+  <si>
+    <t>Internal Auditor</t>
+  </si>
+  <si>
+    <t>JOB-000018</t>
+  </si>
+  <si>
+    <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
+  </si>
+  <si>
+    <t>Cash management reports, investment plans</t>
+  </si>
+  <si>
+    <t>Treasurers manage a company's financial assets, including cash flow, investments, and risk management strategies.</t>
+  </si>
+  <si>
+    <t>Treasurer</t>
+  </si>
+  <si>
+    <t>JOB-000017</t>
+  </si>
+  <si>
+    <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
+  </si>
+  <si>
+    <t>Financial models, market analysis</t>
+  </si>
+  <si>
+    <t>Financial analysts analyze market trends, financial data, and economic conditions to provide investment and business recommendations.</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000016</t>
+  </si>
+  <si>
+    <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
+  </si>
+  <si>
+    <t>Budget reports, financial forecasts</t>
+  </si>
+  <si>
+    <t>Controllers oversee financial operations, ensuring compliance and efficiency. They manage budgeting, forecasting, and financial reporting within an organization.</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>JOB-000015</t>
+  </si>
+  <si>
+    <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
+  </si>
+  <si>
+    <t>Financial statements, tax filings</t>
+  </si>
+  <si>
+    <t>Accountants manage financial records, ensuring accuracy and compliance with regulations. They prepare reports, handle taxes, and assist with budgeting.</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>JOB-000014</t>
+  </si>
+  <si>
+    <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
+  </si>
+  <si>
+    <t>Statistical models, reports, insights</t>
+  </si>
+  <si>
+    <t>Statisticians analyze and interpret data to identify trends and patterns. They design surveys and experiments, and use statistical models to inform decision-making.</t>
+  </si>
+  <si>
+    <t>Statistician</t>
+  </si>
+  <si>
+    <t>JOB-000005</t>
+  </si>
+  <si>
+    <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
+  </si>
+  <si>
+    <t>Game launch, marketing materials, distribution</t>
+  </si>
+  <si>
+    <t>Publishing producers manage the relationship between game development teams and publishers, overseeing the release, marketing, and distribution of games.</t>
+  </si>
+  <si>
+    <t>Game Publisher - Publishing Producer</t>
+  </si>
+  <si>
+    <t>JOB-000004</t>
+  </si>
+  <si>
+    <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
+  </si>
+  <si>
+    <t>Software systems, applications, features</t>
+  </si>
+  <si>
+    <t>Software engineers apply engineering principles to software development, focusing on the development and maintenance of software systems and applications.</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000003</t>
+  </si>
+  <si>
+    <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
+  </si>
+  <si>
+    <t>Prototypes, technical reports</t>
+  </si>
+  <si>
+    <t>R&amp;D engineers design and develop new products or technologies, conducting experiments and testing prototypes for functionality and feasibility.</t>
+  </si>
+  <si>
+    <t>R&amp;D Engineer</t>
+  </si>
+  <si>
+    <t>JOB-000002</t>
+  </si>
+  <si>
+    <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
+  </si>
+  <si>
+    <t>Financial strategy, risk management plans</t>
+  </si>
+  <si>
+    <t>The CFO oversees the financial operations of an organization, ensuring strategic financial planning, risk management, and compliance with regulations.</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer (CFO)</t>
+  </si>
+  <si>
+    <t>JOB-000013</t>
+  </si>
+  <si>
+    <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
+  </si>
+  <si>
+    <t>Business strategy reports, market trend analysis</t>
+  </si>
+  <si>
+    <t>Strategy analysts provide insights and recommendations to guide the company's strategic direction, using data and competitive analysis to inform decisions.</t>
+  </si>
+  <si>
+    <t>Strategy Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000012</t>
+  </si>
+  <si>
+    <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
+  </si>
+  <si>
+    <t>Mergers and acquisitions, strategic partnerships</t>
+  </si>
+  <si>
+    <t>Corporate development managers identify new business opportunities, partnerships, and strategic acquisitions to drive growth and expansion for the company.</t>
+  </si>
+  <si>
+    <t>Corporate Development Manager</t>
+  </si>
+  <si>
+    <t>JOB-000011</t>
+  </si>
+  <si>
+    <t>Excel, SAP, POS systems, CRM software</t>
+  </si>
+  <si>
+    <t>Franchise operational standards, profitability metrics</t>
+  </si>
+  <si>
+    <t>Franchise managers oversee the operations of franchise locations, ensuring brand standards, profitability, and compliance are maintained across locations.</t>
+  </si>
+  <si>
+    <t>Franchise Manager</t>
+  </si>
+  <si>
+    <t>JOB-000010</t>
+  </si>
+  <si>
+    <t>JIRA, Confluence, Trello, Slack, Aha!</t>
+  </si>
+  <si>
+    <t>Product backlog, feature requirements, sprint planning</t>
+  </si>
+  <si>
+    <t>Product owners work with development teams to ensure that product features and requirements are clearly defined and aligned with business priorities.</t>
+  </si>
+  <si>
+    <t>Product Owner</t>
+  </si>
+  <si>
+    <t>JOB-000009</t>
+  </si>
+  <si>
+    <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
+  </si>
+  <si>
+    <t>Product roadmap, feature prioritization, go-to-market strategy</t>
+  </si>
+  <si>
+    <t>Product managers oversee the development and lifecycle of a product, from ideation to launch, ensuring it meets customer needs and business goals.</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>JOB-000008</t>
+  </si>
+  <si>
+    <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
+  </si>
+  <si>
+    <t>Supply chain efficiency, inventory management reports</t>
+  </si>
+  <si>
+    <t>Supply chain analysts track and optimize the movement of goods and materials throughout the supply chain, identifying efficiencies and areas for improvement.</t>
+  </si>
+  <si>
+    <t>Supply Chain Analyst</t>
+  </si>
+  <si>
+    <t>JOB-000007</t>
+  </si>
+  <si>
+    <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
+  </si>
+  <si>
+    <t>Supplier contracts, cost-efficient procurement strategies</t>
+  </si>
+  <si>
+    <t>Procurement specialists manage the sourcing of materials or services needed by a company, ensuring quality, cost-efficiency, and timely delivery from suppliers.</t>
+  </si>
+  <si>
+    <t>Procurement Specialist</t>
+  </si>
+  <si>
+    <t>JOB-000006</t>
+  </si>
+  <si>
+    <t>Excel, SAP, Microsoft Project, Vendor management software</t>
+  </si>
+  <si>
+    <t>Vendor contracts, service agreements, cost-saving initiatives</t>
+  </si>
+  <si>
+    <t>Outsourcing managers are responsible for managing the relationship with external vendors and service providers, ensuring services are delivered on time and within budget.</t>
+  </si>
+  <si>
+    <t>Outsourcing Manager</t>
+  </si>
+  <si>
+    <t>JOB-000001</t>
+  </si>
+  <si>
+    <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
+  </si>
+  <si>
+    <t>Product insights, data reports, market analysis</t>
+  </si>
+  <si>
+    <t>Product analysts assess market trends, customer needs, and product performance. They use data to make recommendations for product improvements or new launches.</t>
+  </si>
+  <si>
+    <t>Product Analyst</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,21 +1573,31 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -104,8 +1614,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,56 +1920,1757 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K101"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B9" t="s">
+        <v>470</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B12" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" t="s">
+        <v>450</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B14" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" t="s">
+        <v>430</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B18" t="s">
+        <v>425</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20" t="s">
+        <v>415</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B21" t="s">
+        <v>410</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" t="s">
+        <v>405</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B23" t="s">
+        <v>400</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B24" t="s">
+        <v>395</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B25" t="s">
+        <v>390</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B26" t="s">
+        <v>385</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B27" t="s">
+        <v>380</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B29" t="s">
+        <v>370</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B30" t="s">
+        <v>365</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B31" t="s">
+        <v>360</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B33" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B34" t="s">
+        <v>345</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" t="s">
+        <v>340</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" t="s">
+        <v>335</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B37" t="s">
+        <v>330</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B39" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B40" t="s">
+        <v>315</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>310</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B42" t="s">
+        <v>305</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B43" t="s">
+        <v>300</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B44" t="s">
+        <v>295</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B45" t="s">
+        <v>290</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B46" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B47" t="s">
+        <v>280</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B48" t="s">
+        <v>275</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" t="s">
+        <v>270</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B50" t="s">
+        <v>265</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B51" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" t="s">
+        <v>250</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B54" t="s">
+        <v>245</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" t="s">
+        <v>235</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B57" t="s">
+        <v>230</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B58" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B59" t="s">
+        <v>220</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" t="s">
+        <v>215</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" t="s">
+        <v>195</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" t="s">
+        <v>170</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" t="s">
+        <v>160</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" t="s">
+        <v>156</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" t="s">
+        <v>151</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B79" t="s">
+        <v>121</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B80" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>81</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" t="s">
+        <v>76</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B89" t="s">
+        <v>71</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B91" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B92" t="s">
+        <v>56</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C996" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"PRIVATE_SECTOR,PUBLIC_SECTOR,GOVERNMENT,NGO,MILITARY,ACADEMIC,OTHER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E996" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"INTERN,JUNIOR,MID,SENIOR,LEAD,DIRECTOR,C_LEVEL,ELECTED,OTHER"</formula1>
     </dataValidation>
   </dataValidations>

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F5BCA-2AEF-FE49-81CC-9569A046230A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B916F7-3C44-5F45-A202-067E62B80D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jobs" sheetId="1" r:id="rId1"/>
@@ -1923,9 +1923,12 @@
   <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="11" width="18" customWidth="1"/>
+    <col min="1" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="138.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -3822,7 +3822,7 @@
       <c r="K101" s="3" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:K1"/>
   <dataValidations count="3">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -506,7 +506,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:K1"/>
   <dataValidations count="3">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,6 +67,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -504,6 +507,3306 @@
           <t>score</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Product analysts assess market trends, customer needs, and product performance. They use data to make recommendations for product improvements or new launches.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Product insights, data reports, market analysis</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Outsourcing Manager</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000006</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Outsourcing managers are responsible for managing the relationship with external vendors and service providers, ensuring services are delivered on time and within budget.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Vendor contracts, service agreements, cost-saving initiatives</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Excel, SAP, Microsoft Project, Vendor management software</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Procurement Specialist</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000007</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Procurement specialists manage the sourcing of materials or services needed by a company, ensuring quality, cost-efficiency, and timely delivery from suppliers.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Supplier contracts, cost-efficient procurement strategies</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Supply Chain Analyst</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000008</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Supply chain analysts track and optimize the movement of goods and materials throughout the supply chain, identifying efficiencies and areas for improvement.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Supply chain efficiency, inventory management reports</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000009</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Product managers oversee the development and lifecycle of a product, from ideation to launch, ensuring it meets customer needs and business goals.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Product roadmap, feature prioritization, go-to-market strategy</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000010</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Product owners work with development teams to ensure that product features and requirements are clearly defined and aligned with business priorities.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Product backlog, feature requirements, sprint planning</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>JIRA, Confluence, Trello, Slack, Aha!</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Franchise Manager</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000011</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Franchise managers oversee the operations of franchise locations, ensuring brand standards, profitability, and compliance are maintained across locations.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Franchise operational standards, profitability metrics</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Excel, SAP, POS systems, CRM software</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Corporate Development Manager</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000012</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Corporate development managers identify new business opportunities, partnerships, and strategic acquisitions to drive growth and expansion for the company.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Mergers and acquisitions, strategic partnerships</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Strategy Analyst</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000013</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Strategy analysts provide insights and recommendations to guide the company's strategic direction, using data and competitive analysis to inform decisions.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Business strategy reports, market trend analysis</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer (CFO)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000002</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>The CFO oversees the financial operations of an organization, ensuring strategic financial planning, risk management, and compliance with regulations.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Financial strategy, risk management plans</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>R&amp;D Engineer</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000003</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>R&amp;D engineers design and develop new products or technologies, conducting experiments and testing prototypes for functionality and feasibility.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Prototypes, technical reports</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000004</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Software engineers apply engineering principles to software development, focusing on the development and maintenance of software systems and applications.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Software systems, applications, features</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Game Publisher - Publishing Producer</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000005</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Publishing producers manage the relationship between game development teams and publishers, overseeing the release, marketing, and distribution of games.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Game launch, marketing materials, distribution</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Statistician</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000014</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Statisticians analyze and interpret data to identify trends and patterns. They design surveys and experiments, and use statistical models to inform decision-making.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Statistical models, reports, insights</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000015</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Accountants manage financial records, ensuring accuracy and compliance with regulations. They prepare reports, handle taxes, and assist with budgeting.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Financial statements, tax filings</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000016</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Controllers oversee financial operations, ensuring compliance and efficiency. They manage budgeting, forecasting, and financial reporting within an organization.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Budget reports, financial forecasts</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000017</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Financial analysts analyze market trends, financial data, and economic conditions to provide investment and business recommendations.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Financial models, market analysis</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Treasurer</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000018</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Treasurers manage a company's financial assets, including cash flow, investments, and risk management strategies.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Cash management reports, investment plans</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Internal Auditor</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000019</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Internal auditors review and evaluate financial and operational processes to ensure compliance, efficiency, and risk mitigation within an organization.</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Audit reports, compliance reviews</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Compliance Manager</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000020</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Compliance managers develop and enforce policies to ensure an organization adheres to laws, regulations, and internal standards.</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Compliance reports, policy guidelines</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Compliance Officer</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000021</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Compliance officers monitor and report on organizational adherence to legal standards, ensuring that financial and operational activities meet regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Compliance audit reports, risk assessments</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate Analyst</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000022</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Real estate analysts assess property values, market trends, and investment opportunities, providing data-driven recommendations for investment decisions.</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Market analysis reports, property valuations</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Risk Analyst</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000023</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Risk analysts identify, evaluate, and manage financial and operational risks, using quantitative methods to protect an organization's assets.</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Risk models, risk assessments</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000024</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Administrative coordinators manage daily office tasks, including scheduling, correspondence, and organizing meetings and events.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Schedules, event planning, reports</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Executive assistants support high-level executives by managing their calendars, arranging meetings, and performing administrative duties.</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Calendar schedules, meeting agendas</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Office Assistant</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Office assistants handle basic administrative tasks such as answering phones, organizing files, and assisting with office operations.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Filing systems, office organization</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Google Workspace, Excel, Word</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Office Head</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000027</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>The office head oversees office operations, including managing staff, budgets, and overall office efficiency.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Office management reports, team coordination</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Office Manager</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000028</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Office managers supervise office functions, ensure smooth operations, manage supplies, and support administrative teams.</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Office systems, inventory management</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Graphic Designer</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Graphic designers create visual content, from logos and websites to marketing materials, ensuring they align with brand identity.</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Logos, brochures, websites, advertisements</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Civil Engineer</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000030</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Civil engineers design, plan, and oversee construction projects like roads, bridges, and buildings, ensuring safety, functionality, and environmental impact.</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Construction blueprints, project plans</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Electrical Engineer</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000031</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Electrical engineers design and test electrical systems and equipment, ensuring efficiency and safety in applications ranging from consumer electronics to power grids.</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Electrical schematics, system designs</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000032</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical engineers design, analyze, and manufacture mechanical systems, ensuring functionality and durability in industries like automotive and manufacturing.</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Product prototypes, mechanical designs</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Process Engineer</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000033</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Process engineers design, implement, and optimize industrial processes in manufacturing and production to ensure efficiency, quality, and cost-effectiveness.</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Optimized production processes, cost savings</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Team Lead</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000034</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Team leads supervise and guide team members to meet goals, improve productivity, and foster a collaborative work environment.</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Team performance, project results</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Interpreter-Translator</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000035</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Interpreters and translators convert spoken or written content from one language to another, ensuring accuracy and cultural sensitivity.</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Translated documents, verbal translations</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Language Lead</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000036</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Language leads oversee translation projects, manage teams of translators, and ensure quality and accuracy in linguistic services across various languages.</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Translated materials, multilingual content</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Facilities Manager</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000037</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Facilities managers oversee the day-to-day operations of an organization's physical workspace, ensuring maintenance, safety, and efficiency.</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance schedules, facility reports</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000038</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Logistics coordinators manage the supply chain, ensuring the timely and cost-effective transportation and storage of goods.</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Shipping schedules, inventory reports</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance Supervisor</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000039</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance supervisors oversee the maintenance and repair of equipment and facilities, ensuring smooth operational flow.</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Equipment repair logs, maintenance schedules</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000040</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Operations managers oversee all aspects of daily business activities, optimizing processes to enhance efficiency, reduce costs, and improve performance.</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Operational reports, process optimization</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Plant Manager</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000041</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Plant managers oversee manufacturing facilities, ensuring efficient production, safety, and compliance with regulations.</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Production schedules, plant safety records</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000042</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Production supervisors manage the daily activities of production workers, ensuring product quality and on-time completion.</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Production output, quality control reports</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Excel, MES software, SAP, Production scheduling tools</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000043</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Project managers plan, execute, and close projects, ensuring they are completed on time, within scope, and within budget.</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Project plans, timelines, budget reports</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Quality Control Analyst</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000044</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Quality control analysts test and inspect products or processes to ensure they meet established standards and regulations.</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Quality reports, inspection logs</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Lab Technician</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000045</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Lab technicians conduct scientific experiments, maintain equipment, and analyze data to assist in research and development projects.</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Research findings, test results</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Business Planner</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000046</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Business planners develop strategic plans that align company goals with market opportunities, analyzing trends and forecasts.</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Business plans, market analysis reports</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Compensation and Benefits Specialist</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000047</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Compensation and benefits specialists manage employee pay, benefits packages, and compensation plans, ensuring compliance and competitiveness.</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Compensation reports, benefits strategies</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>HR Generalist</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000048</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>HR generalists handle various HR functions, including recruitment, employee relations, performance management, and policy implementation.</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Employee records, performance reviews</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000049</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>HR managers oversee HR teams, ensuring the effective management of recruitment, training, employee relations, and performance management.</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>HR strategy reports, employee programs</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>HR Recruiter</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000050</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>HR recruiters source, screen, and hire talent for an organization, managing the recruitment process from job postings to interviews.</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Recruitment reports, candidate pipelines</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000051</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Recruiters focus on finding and attracting qualified candidates for job openings, guiding them through the hiring process.</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Job offers, candidate databases</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000052</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>HR business partners work closely with business leaders to align HR practices with business goals, focusing on workforce planning, development, and strategy.</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>HR strategy reports, talent management plans</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Ethics Officer</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000053</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Ethics officers develop and enforce ethical guidelines, ensuring compliance with laws and regulations within an organization.</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Ethics policies, compliance reports</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>AI Programmer</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000054</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>AI programmers design and implement artificial intelligence algorithms and systems, creating intelligent solutions for a range of applications.</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>AI models, machine learning algorithms</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>AI Research Scientist</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000055</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>AI research scientists conduct advanced research in artificial intelligence, developing new methodologies and pushing the boundaries of machine learning and AI.</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Research papers, AI algorithms</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Analytics Manager</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000056</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Analytics managers oversee data analytics teams, guiding them in deriving actionable insights from large datasets to inform business decisions.</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Analytics reports, data insights</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Android Developer</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000057</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Android developers create mobile applications for Android devices, ensuring seamless user experiences and integration with various device features.</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Android apps, mobile solutions</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>AR VR Developer</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000058</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>AR/VR developers design and implement augmented and virtual reality experiences, creating immersive environments for entertainment, training, and other applications.</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>AR/VR apps, immersive experiences</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Augmented Reality (AR) Programmer</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000059</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>AR programmers develop software that overlays digital content onto the real world, enhancing user interactions through augmented reality technology.</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>AR applications, interactive content</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Back-End Developer</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000060</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Back-end developers focus on server-side programming, building and maintaining the infrastructure that supports web applications and databases.</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Web services, APIs, server-side systems</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000061</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Business Intelligence (BI) developers design and implement systems that help organizations analyze and interpret data to improve decision-making.</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>BI dashboards, reporting tools</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Big Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000062</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Big Data engineers design and manage systems for processing and analyzing large sets of structured and unstructured data across distributed systems.</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Big Data platforms, data pipelines</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain Developer</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000063</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain developers create decentralized applications and blockchain platforms, focusing on secure transactions and data integrity using distributed ledger technology.</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Blockchain apps, decentralized solutions</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000064</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>BI analysts evaluate and interpret data to provide insights and recommendations that guide business strategy and improve performance.</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Data reports, business insights</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000065</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>BI developers design and implement the infrastructure for data analysis, creating dashboards, reports, and other tools for decision-making.</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>BI systems, reporting solutions</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Business Objects Developer</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000066</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Business Objects developers create and manage business intelligence applications, focusing on data integration, reporting, and analytics.</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Reports, dashboards, data analysis</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000067</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Business analysts assess business processes and identify opportunities for improvement, translating business needs into technical solutions.</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Requirements documents, business solutions</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Chief Information Officer (CIO)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000068</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>The CIO oversees the IT strategy and operations of an organization, ensuring technology aligns with business goals and drives innovation.</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>IT strategy, technology roadmaps</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000069</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Cloud engineers design, implement, and maintain cloud-based solutions, ensuring scalability, security, and performance across cloud environments.</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Cloud infrastructure, cloud services</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Cross-Platform Developer</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000070</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Cross-platform developers build applications that run seamlessly on multiple operating systems, reducing development time and cost.</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Multi-platform apps, mobile/web solutions</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity Analyst</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000071</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Cybersecurity analysts protect an organization's systems and data from cyber threats by monitoring for security breaches, vulnerabilities, and attacks.</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Security protocols, vulnerability reports</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000072</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Data analysts interpret complex data to help organizations make data-driven decisions, often working with raw data and presenting findings to stakeholders.</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Data reports, data visualizations</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Data Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000073</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Data analytics consultants help organizations optimize their data strategy, analyzing business data to provide actionable insights for growth.</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Analytics reports, recommendations</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000074</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Data architects design and structure data systems, ensuring that data is accessible, secure, and scalable across various platforms and applications.</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Data architecture, data models</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Data Center Engineer</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000075</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Data center engineers manage and maintain the physical and virtual infrastructure of data centers, ensuring high availability, performance, and security.</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Data center infrastructure, network systems</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000076</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Data engineers design, build, and maintain data pipelines and infrastructure, ensuring smooth flow and storage of data for analysis.</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Data pipelines, data storage systems</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Data Modeler</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000077</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Data modelers design data models, structures, and databases, ensuring that data is stored efficiently and can be easily accessed for analysis.</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Data models, data structures</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000078</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Data scientists analyze complex data sets using advanced statistical, mathematical, and programming techniques to build models and predictions.</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Predictive models, machine learning algorithms</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Database Administrator (DBA)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000079</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>DBAs manage and maintain databases, ensuring their performance, integrity, and security while troubleshooting and resolving issues.</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Database performance, backups, security</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Database Support Specialist</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000080</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Database support specialists provide technical support for database systems, troubleshooting issues and ensuring smooth operations.</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Database maintenance, troubleshooting</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Database Tester</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000081</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Database testers validate and test databases to ensure data accuracy, integrity, and functionality by executing test cases and identifying bugs.</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Test reports, database issues</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Datawarehouse Specialist</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000082</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Data warehouse specialists design, implement, and manage large-scale data storage systems, ensuring that data is organized, accessible, and optimized for analysis.</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Data warehouses, ETL pipelines</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Deep Learning Specialist</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000083</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Deep learning specialists focus on advanced machine learning techniques, creating neural networks and AI models for tasks like image recognition and natural language processing.</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Deep learning models, AI applications</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Desktop Support Technician</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000084</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Desktop support technicians troubleshoot and resolve hardware and software issues on desktops and laptops, providing technical support to end users.</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Resolved technical issues, support tickets</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="5" t="n"/>
+      <c r="K85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000085</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>DevOps engineers automate and streamline the deployment, integration, and monitoring of applications and infrastructure, ensuring faster development cycles.</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Continuous integration pipelines, deployment automation</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="5" t="n"/>
+      <c r="K86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000086</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>ETL (Extract, Transform, Load) developers design and manage data workflows to extract data from various sources, transform it into a usable format, and load it into databases.</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>ETL pipelines, data transformations</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Extended Reality (XR) Programmer</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000087</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>XR programmers create immersive experiences using augmented reality (AR), virtual reality (VR), and mixed reality (MR), developing applications for various industries.</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>XR applications, immersive experiences</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Front-End Developer</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000088</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Front-end developers design and build the user-facing components of websites and applications, ensuring responsive design and user experience.</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Websites, user interfaces, web apps</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000089</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Full-stack developers handle both the front-end and back-end of web applications, ensuring smooth communication between the user interface and databases.</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Full web applications, APIs, services</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Informatica Developer</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000090</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Informatica developers design and implement data integration solutions using Informatica tools to facilitate data movement and transformation across platforms.</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>ETL processes, data integrations</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Information Security Analyst</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000091</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Information security analysts assess and secure an organization's IT infrastructure by identifying vulnerabilities, monitoring systems, and responding to incidents.</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Security protocols, vulnerability reports</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Information Security Officer</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000092</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Information security officers develop and enforce policies to protect sensitive data and networks from internal and external threats.</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Security policies, compliance reports</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000093</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure architects design and manage the underlying IT infrastructure, ensuring that systems are scalable, secure, and reliable to support business operations.</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>IT infrastructure, architecture plans</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="5" t="n"/>
+      <c r="K94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>iOS Developer</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000094</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>iOS developers create applications for Apple's ecosystem, ensuring a seamless user experience across iPhones, iPads, and other Apple devices.</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>iOS apps, mobile solutions</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>IoT Specialist</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000095</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>IoT specialists design and manage interconnected systems and devices, ensuring secure data transfer and real-time functionality for the Internet of Things.</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>IoT solutions, connected devices</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>IT Support Specialist</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000096</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>IT support specialists provide technical assistance for users, troubleshooting hardware/software issues and maintaining systems and networks.</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Technical support tickets, system maintenance</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+      <c r="K97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>IT Technician</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000097</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>IT technicians install, configure, and maintain hardware and software systems, assisting users and ensuring smooth operation of company devices and systems.</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Hardware setup, software installation</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000098</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Machine learning engineers develop algorithms that allow systems to improve over time based on data, working with large datasets to build predictive models.</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Machine learning models, data-driven insights</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="n"/>
+      <c r="K99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>MicroStrategy Developer</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000099</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>MicroStrategy developers design and implement business intelligence solutions using the MicroStrategy platform, focusing on reporting and data analysis.</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>BI reports, data analytics platforms</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="5" t="n"/>
+      <c r="K100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Mixed Reality (MR) Programmer</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>JOB-000100</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>MR programmers develop interactive and immersive experiences using both virtual and augmented reality, blending the real and virtual worlds.</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>MR applications, interactive content</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,9 +67,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,3304 +506,2704 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Product Analyst</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>JOB-000001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Product analysts assess market trends, customer needs, and product performance. They use data to make recommendations for product improvements or new launches.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Product insights, data reports, market analysis</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Outsourcing Manager</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>JOB-000006</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Outsourcing managers are responsible for managing the relationship with external vendors and service providers, ensuring services are delivered on time and within budget.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Vendor contracts, service agreements, cost-saving initiatives</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Excel, SAP, Microsoft Project, Vendor management software</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Procurement Specialist</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>JOB-000007</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Procurement specialists manage the sourcing of materials or services needed by a company, ensuring quality, cost-efficiency, and timely delivery from suppliers.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Supplier contracts, cost-efficient procurement strategies</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>JOB-000008</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Supply chain analysts track and optimize the movement of goods and materials throughout the supply chain, identifying efficiencies and areas for improvement.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Supply chain efficiency, inventory management reports</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>JOB-000009</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Product managers oversee the development and lifecycle of a product, from ideation to launch, ensuring it meets customer needs and business goals.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Product roadmap, feature prioritization, go-to-market strategy</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>JOB-000010</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Product owners work with development teams to ensure that product features and requirements are clearly defined and aligned with business priorities.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Product backlog, feature requirements, sprint planning</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>JIRA, Confluence, Trello, Slack, Aha!</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Franchise Manager</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>JOB-000011</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Franchise managers oversee the operations of franchise locations, ensuring brand standards, profitability, and compliance are maintained across locations.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Franchise operational standards, profitability metrics</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Excel, SAP, POS systems, CRM software</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Corporate Development Manager</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>JOB-000012</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Corporate development managers identify new business opportunities, partnerships, and strategic acquisitions to drive growth and expansion for the company.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Mergers and acquisitions, strategic partnerships</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Strategy Analyst</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>JOB-000013</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Strategy analysts provide insights and recommendations to guide the company's strategic direction, using data and competitive analysis to inform decisions.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Business strategy reports, market trend analysis</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Chief Financial Officer (CFO)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>JOB-000002</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>The CFO oversees the financial operations of an organization, ensuring strategic financial planning, risk management, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Financial strategy, risk management plans</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>R&amp;D Engineer</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>JOB-000003</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>R&amp;D engineers design and develop new products or technologies, conducting experiments and testing prototypes for functionality and feasibility.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Prototypes, technical reports</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>JOB-000004</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Software engineers apply engineering principles to software development, focusing on the development and maintenance of software systems and applications.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Software systems, applications, features</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Game Publisher - Publishing Producer</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>JOB-000005</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Publishing producers manage the relationship between game development teams and publishers, overseeing the release, marketing, and distribution of games.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Game launch, marketing materials, distribution</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Statistician</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>JOB-000014</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Statisticians analyze and interpret data to identify trends and patterns. They design surveys and experiments, and use statistical models to inform decision-making.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Statistical models, reports, insights</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Accountant</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>JOB-000015</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Accountants manage financial records, ensuring accuracy and compliance with regulations. They prepare reports, handle taxes, and assist with budgeting.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Financial statements, tax filings</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>JOB-000016</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Controllers oversee financial operations, ensuring compliance and efficiency. They manage budgeting, forecasting, and financial reporting within an organization.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Budget reports, financial forecasts</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>JOB-000017</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Financial analysts analyze market trends, financial data, and economic conditions to provide investment and business recommendations.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Financial models, market analysis</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Treasurer</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>JOB-000018</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Treasurers manage a company's financial assets, including cash flow, investments, and risk management strategies.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Cash management reports, investment plans</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Internal Auditor</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>JOB-000019</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Internal auditors review and evaluate financial and operational processes to ensure compliance, efficiency, and risk mitigation within an organization.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Audit reports, compliance reviews</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Compliance Manager</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>JOB-000020</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Compliance managers develop and enforce policies to ensure an organization adheres to laws, regulations, and internal standards.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Compliance reports, policy guidelines</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Compliance Officer</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>JOB-000021</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Compliance officers monitor and report on organizational adherence to legal standards, ensuring that financial and operational activities meet regulatory requirements.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Compliance audit reports, risk assessments</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Real Estate Analyst</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>JOB-000022</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Real estate analysts assess property values, market trends, and investment opportunities, providing data-driven recommendations for investment decisions.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Market analysis reports, property valuations</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Risk Analyst</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>JOB-000023</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Risk analysts identify, evaluate, and manage financial and operational risks, using quantitative methods to protect an organization's assets.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Risk models, risk assessments</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Administrative Coordinator</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>JOB-000024</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Administrative coordinators manage daily office tasks, including scheduling, correspondence, and organizing meetings and events.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Schedules, event planning, reports</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Executive Assistant</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>JOB-000025</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Executive assistants support high-level executives by managing their calendars, arranging meetings, and performing administrative duties.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Calendar schedules, meeting agendas</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Office Assistant</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>JOB-000026</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Office assistants handle basic administrative tasks such as answering phones, organizing files, and assisting with office operations.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Filing systems, office organization</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Excel, Word</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Office Head</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>JOB-000027</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>The office head oversees office operations, including managing staff, budgets, and overall office efficiency.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Office management reports, team coordination</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Office Manager</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>JOB-000028</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Office managers supervise office functions, ensure smooth operations, manage supplies, and support administrative teams.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Office systems, inventory management</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Graphic Designer</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>JOB-000029</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Graphic designers create visual content, from logos and websites to marketing materials, ensuring they align with brand identity.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Logos, brochures, websites, advertisements</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Civil Engineer</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>JOB-000030</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Civil engineers design, plan, and oversee construction projects like roads, bridges, and buildings, ensuring safety, functionality, and environmental impact.</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Construction blueprints, project plans</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Electrical Engineer</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>JOB-000031</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Electrical engineers design and test electrical systems and equipment, ensuring efficiency and safety in applications ranging from consumer electronics to power grids.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Electrical schematics, system designs</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Mechanical Engineer</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>JOB-000032</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Mechanical engineers design, analyze, and manufacture mechanical systems, ensuring functionality and durability in industries like automotive and manufacturing.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Product prototypes, mechanical designs</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Process Engineer</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>JOB-000033</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Process engineers design, implement, and optimize industrial processes in manufacturing and production to ensure efficiency, quality, and cost-effectiveness.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Optimized production processes, cost savings</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>JOB-000034</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Team leads supervise and guide team members to meet goals, improve productivity, and foster a collaborative work environment.</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Team performance, project results</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Interpreter-Translator</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>JOB-000035</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Interpreters and translators convert spoken or written content from one language to another, ensuring accuracy and cultural sensitivity.</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Translated documents, verbal translations</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Language Lead</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>JOB-000036</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Language leads oversee translation projects, manage teams of translators, and ensure quality and accuracy in linguistic services across various languages.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Translated materials, multilingual content</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Facilities Manager</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>JOB-000037</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Facilities managers oversee the day-to-day operations of an organization's physical workspace, ensuring maintenance, safety, and efficiency.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Maintenance schedules, facility reports</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Logistics Coordinator</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>JOB-000038</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Logistics coordinators manage the supply chain, ensuring the timely and cost-effective transportation and storage of goods.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Shipping schedules, inventory reports</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Maintenance Supervisor</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>JOB-000039</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Maintenance supervisors oversee the maintenance and repair of equipment and facilities, ensuring smooth operational flow.</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Equipment repair logs, maintenance schedules</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Operations Manager</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>JOB-000040</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Operations managers oversee all aspects of daily business activities, optimizing processes to enhance efficiency, reduce costs, and improve performance.</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Operational reports, process optimization</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Plant Manager</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>JOB-000041</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Plant managers oversee manufacturing facilities, ensuring efficient production, safety, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Production schedules, plant safety records</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>JOB-000042</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Production supervisors manage the daily activities of production workers, ensuring product quality and on-time completion.</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Production output, quality control reports</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Excel, MES software, SAP, Production scheduling tools</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>JOB-000043</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Project managers plan, execute, and close projects, ensuring they are completed on time, within scope, and within budget.</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Project plans, timelines, budget reports</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Quality Control Analyst</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>JOB-000044</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Quality control analysts test and inspect products or processes to ensure they meet established standards and regulations.</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Quality reports, inspection logs</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Lab Technician</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>JOB-000045</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Lab technicians conduct scientific experiments, maintain equipment, and analyze data to assist in research and development projects.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Research findings, test results</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Business Planner</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>JOB-000046</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Business planners develop strategic plans that align company goals with market opportunities, analyzing trends and forecasts.</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Business plans, market analysis reports</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Compensation and Benefits Specialist</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>JOB-000047</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Compensation and benefits specialists manage employee pay, benefits packages, and compensation plans, ensuring compliance and competitiveness.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Compensation reports, benefits strategies</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>JOB-000048</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>HR generalists handle various HR functions, including recruitment, employee relations, performance management, and policy implementation.</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Employee records, performance reviews</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
         </is>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>JOB-000049</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>HR managers oversee HR teams, ensuring the effective management of recruitment, training, employee relations, and performance management.</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>HR strategy reports, employee programs</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>HR Recruiter</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>JOB-000050</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>HR recruiters source, screen, and hire talent for an organization, managing the recruitment process from job postings to interviews.</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Recruitment reports, candidate pipelines</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Recruiter</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>JOB-000051</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Recruiters focus on finding and attracting qualified candidates for job openings, guiding them through the hiring process.</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Job offers, candidate databases</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>JOB-000052</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>HR business partners work closely with business leaders to align HR practices with business goals, focusing on workforce planning, development, and strategy.</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>HR strategy reports, talent management plans</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
         </is>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Ethics Officer</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>JOB-000053</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Ethics officers develop and enforce ethical guidelines, ensuring compliance with laws and regulations within an organization.</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Ethics policies, compliance reports</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>AI Programmer</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>JOB-000054</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>AI programmers design and implement artificial intelligence algorithms and systems, creating intelligent solutions for a range of applications.</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>AI models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>AI Research Scientist</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>JOB-000055</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>AI research scientists conduct advanced research in artificial intelligence, developing new methodologies and pushing the boundaries of machine learning and AI.</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Research papers, AI algorithms</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Analytics Manager</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>JOB-000056</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Analytics managers oversee data analytics teams, guiding them in deriving actionable insights from large datasets to inform business decisions.</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Analytics reports, data insights</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Android Developer</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>JOB-000057</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Android developers create mobile applications for Android devices, ensuring seamless user experiences and integration with various device features.</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Android apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>AR VR Developer</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>JOB-000058</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>AR/VR developers design and implement augmented and virtual reality experiences, creating immersive environments for entertainment, training, and other applications.</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>AR/VR apps, immersive experiences</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Augmented Reality (AR) Programmer</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>JOB-000059</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>AR programmers develop software that overlays digital content onto the real world, enhancing user interactions through augmented reality technology.</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>AR applications, interactive content</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Back-End Developer</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>JOB-000060</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Back-end developers focus on server-side programming, building and maintaining the infrastructure that supports web applications and databases.</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Web services, APIs, server-side systems</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>BI Developer</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>JOB-000061</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Business Intelligence (BI) developers design and implement systems that help organizations analyze and interpret data to improve decision-making.</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BI dashboards, reporting tools</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Big Data Engineer</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>JOB-000062</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Big Data engineers design and manage systems for processing and analyzing large sets of structured and unstructured data across distributed systems.</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Big Data platforms, data pipelines</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Blockchain Developer</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>JOB-000063</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Blockchain developers create decentralized applications and blockchain platforms, focusing on secure transactions and data integrity using distributed ledger technology.</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Blockchain apps, decentralized solutions</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Business Intelligence Analyst</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>JOB-000064</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>BI analysts evaluate and interpret data to provide insights and recommendations that guide business strategy and improve performance.</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Data reports, business insights</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Business Intelligence Developer</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>JOB-000065</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>BI developers design and implement the infrastructure for data analysis, creating dashboards, reports, and other tools for decision-making.</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>BI systems, reporting solutions</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Business Objects Developer</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>JOB-000066</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Business Objects developers create and manage business intelligence applications, focusing on data integration, reporting, and analytics.</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Reports, dashboards, data analysis</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>JOB-000067</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Business analysts assess business processes and identify opportunities for improvement, translating business needs into technical solutions.</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Requirements documents, business solutions</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Chief Information Officer (CIO)</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>JOB-000068</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>The CIO oversees the IT strategy and operations of an organization, ensuring technology aligns with business goals and drives innovation.</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>IT strategy, technology roadmaps</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>JOB-000069</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Cloud engineers design, implement, and maintain cloud-based solutions, ensuring scalability, security, and performance across cloud environments.</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Cloud infrastructure, cloud services</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Cross-Platform Developer</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>JOB-000070</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Cross-platform developers build applications that run seamlessly on multiple operating systems, reducing development time and cost.</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Multi-platform apps, mobile/web solutions</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>JOB-000071</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Cybersecurity analysts protect an organization's systems and data from cyber threats by monitoring for security breaches, vulnerabilities, and attacks.</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>JOB-000072</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Data analysts interpret complex data to help organizations make data-driven decisions, often working with raw data and presenting findings to stakeholders.</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Data reports, data visualizations</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Data Analytics Consultant</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>JOB-000073</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Data analytics consultants help organizations optimize their data strategy, analyzing business data to provide actionable insights for growth.</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Analytics reports, recommendations</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Data Architect</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>JOB-000074</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Data architects design and structure data systems, ensuring that data is accessible, secure, and scalable across various platforms and applications.</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Data architecture, data models</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Data Center Engineer</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>JOB-000075</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Data center engineers manage and maintain the physical and virtual infrastructure of data centers, ensuring high availability, performance, and security.</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Data center infrastructure, network systems</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>JOB-000076</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Data engineers design, build, and maintain data pipelines and infrastructure, ensuring smooth flow and storage of data for analysis.</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Data pipelines, data storage systems</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Data Modeler</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>JOB-000077</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Data modelers design data models, structures, and databases, ensuring that data is stored efficiently and can be easily accessed for analysis.</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Data models, data structures</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>JOB-000078</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Data scientists analyze complex data sets using advanced statistical, mathematical, and programming techniques to build models and predictions.</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Predictive models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Database Administrator (DBA)</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>JOB-000079</t>
         </is>
       </c>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>DBAs manage and maintain databases, ensuring their performance, integrity, and security while troubleshooting and resolving issues.</t>
         </is>
       </c>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Database performance, backups, security</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Database Support Specialist</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>JOB-000080</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Database support specialists provide technical support for database systems, troubleshooting issues and ensuring smooth operations.</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Database maintenance, troubleshooting</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Database Tester</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>JOB-000081</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Database testers validate and test databases to ensure data accuracy, integrity, and functionality by executing test cases and identifying bugs.</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Test reports, database issues</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Datawarehouse Specialist</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>JOB-000082</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Data warehouse specialists design, implement, and manage large-scale data storage systems, ensuring that data is organized, accessible, and optimized for analysis.</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Data warehouses, ETL pipelines</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Deep Learning Specialist</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>JOB-000083</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Deep learning specialists focus on advanced machine learning techniques, creating neural networks and AI models for tasks like image recognition and natural language processing.</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Deep learning models, AI applications</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Desktop Support Technician</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>JOB-000084</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Desktop support technicians troubleshoot and resolve hardware and software issues on desktops and laptops, providing technical support to end users.</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Resolved technical issues, support tickets</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>JOB-000085</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>DevOps engineers automate and streamline the deployment, integration, and monitoring of applications and infrastructure, ensuring faster development cycles.</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Continuous integration pipelines, deployment automation</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>ETL Developer</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>JOB-000086</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>ETL (Extract, Transform, Load) developers design and manage data workflows to extract data from various sources, transform it into a usable format, and load it into databases.</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>ETL pipelines, data transformations</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Extended Reality (XR) Programmer</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>JOB-000087</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>XR programmers create immersive experiences using augmented reality (AR), virtual reality (VR), and mixed reality (MR), developing applications for various industries.</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>XR applications, immersive experiences</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Front-End Developer</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>JOB-000088</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Front-end developers design and build the user-facing components of websites and applications, ensuring responsive design and user experience.</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Websites, user interfaces, web apps</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Full-Stack Developer</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>JOB-000089</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Full-stack developers handle both the front-end and back-end of web applications, ensuring smooth communication between the user interface and databases.</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Full web applications, APIs, services</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Informatica Developer</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>JOB-000090</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Informatica developers design and implement data integration solutions using Informatica tools to facilitate data movement and transformation across platforms.</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>ETL processes, data integrations</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Information Security Analyst</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>JOB-000091</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Information security analysts assess and secure an organization's IT infrastructure by identifying vulnerabilities, monitoring systems, and responding to incidents.</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Information Security Officer</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>JOB-000092</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Information security officers develop and enforce policies to protect sensitive data and networks from internal and external threats.</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Security policies, compliance reports</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Infrastructure Architect</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>JOB-000093</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Infrastructure architects design and manage the underlying IT infrastructure, ensuring that systems are scalable, secure, and reliable to support business operations.</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>IT infrastructure, architecture plans</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>iOS Developer</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>JOB-000094</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>iOS developers create applications for Apple's ecosystem, ensuring a seamless user experience across iPhones, iPads, and other Apple devices.</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>iOS apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>IoT Specialist</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>JOB-000095</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>IoT specialists design and manage interconnected systems and devices, ensuring secure data transfer and real-time functionality for the Internet of Things.</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>IoT solutions, connected devices</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>IT Support Specialist</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>JOB-000096</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>IT support specialists provide technical assistance for users, troubleshooting hardware/software issues and maintaining systems and networks.</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Technical support tickets, system maintenance</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>IT Technician</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>JOB-000097</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>IT technicians install, configure, and maintain hardware and software systems, assisting users and ensuring smooth operation of company devices and systems.</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Hardware setup, software installation</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
         </is>
       </c>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>JOB-000098</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Machine learning engineers develop algorithms that allow systems to improve over time based on data, working with large datasets to build predictive models.</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Machine learning models, data-driven insights</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
         </is>
       </c>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>MicroStrategy Developer</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>JOB-000099</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>MicroStrategy developers design and implement business intelligence solutions using the MicroStrategy platform, focusing on reporting and data analysis.</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>BI reports, data analytics platforms</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
         </is>
       </c>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Mixed Reality (MR) Programmer</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>JOB-000100</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>MR programmers develop interactive and immersive experiences using both virtual and augmented reality, blending the real and virtual worlds.</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>MR applications, interactive content</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
         </is>
       </c>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,6 +67,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,2704 +509,3304 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Product Analyst</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>JOB-000001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Product analysts assess market trends, customer needs, and product performance. They use data to make recommendations for product improvements or new launches.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Product insights, data reports, market analysis</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
         </is>
       </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Outsourcing Manager</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>JOB-000006</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Outsourcing managers are responsible for managing the relationship with external vendors and service providers, ensuring services are delivered on time and within budget.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Vendor contracts, service agreements, cost-saving initiatives</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Excel, SAP, Microsoft Project, Vendor management software</t>
         </is>
       </c>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Procurement Specialist</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>JOB-000007</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Procurement specialists manage the sourcing of materials or services needed by a company, ensuring quality, cost-efficiency, and timely delivery from suppliers.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Supplier contracts, cost-efficient procurement strategies</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
         </is>
       </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>JOB-000008</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Supply chain analysts track and optimize the movement of goods and materials throughout the supply chain, identifying efficiencies and areas for improvement.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Supply chain efficiency, inventory management reports</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
         </is>
       </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>JOB-000009</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Product managers oversee the development and lifecycle of a product, from ideation to launch, ensuring it meets customer needs and business goals.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Product roadmap, feature prioritization, go-to-market strategy</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
         </is>
       </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>JOB-000010</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Product owners work with development teams to ensure that product features and requirements are clearly defined and aligned with business priorities.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Product backlog, feature requirements, sprint planning</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>JIRA, Confluence, Trello, Slack, Aha!</t>
         </is>
       </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Franchise Manager</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>JOB-000011</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Franchise managers oversee the operations of franchise locations, ensuring brand standards, profitability, and compliance are maintained across locations.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Franchise operational standards, profitability metrics</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Excel, SAP, POS systems, CRM software</t>
         </is>
       </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Corporate Development Manager</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>JOB-000012</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Corporate development managers identify new business opportunities, partnerships, and strategic acquisitions to drive growth and expansion for the company.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Mergers and acquisitions, strategic partnerships</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
         </is>
       </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Strategy Analyst</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>JOB-000013</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Strategy analysts provide insights and recommendations to guide the company's strategic direction, using data and competitive analysis to inform decisions.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Business strategy reports, market trend analysis</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
         </is>
       </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Chief Financial Officer (CFO)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>JOB-000002</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>The CFO oversees the financial operations of an organization, ensuring strategic financial planning, risk management, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Financial strategy, risk management plans</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
         </is>
       </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>R&amp;D Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>JOB-000003</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>R&amp;D engineers design and develop new products or technologies, conducting experiments and testing prototypes for functionality and feasibility.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Prototypes, technical reports</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
         </is>
       </c>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>JOB-000004</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Software engineers apply engineering principles to software development, focusing on the development and maintenance of software systems and applications.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Software systems, applications, features</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
         </is>
       </c>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Game Publisher - Publishing Producer</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>JOB-000005</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Publishing producers manage the relationship between game development teams and publishers, overseeing the release, marketing, and distribution of games.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Game launch, marketing materials, distribution</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
         </is>
       </c>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Statistician</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>JOB-000014</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Statisticians analyze and interpret data to identify trends and patterns. They design surveys and experiments, and use statistical models to inform decision-making.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Statistical models, reports, insights</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
         </is>
       </c>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Accountant</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>JOB-000015</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Accountants manage financial records, ensuring accuracy and compliance with regulations. They prepare reports, handle taxes, and assist with budgeting.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Financial statements, tax filings</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
         </is>
       </c>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>JOB-000016</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Controllers oversee financial operations, ensuring compliance and efficiency. They manage budgeting, forecasting, and financial reporting within an organization.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Budget reports, financial forecasts</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
         </is>
       </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>JOB-000017</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Financial analysts analyze market trends, financial data, and economic conditions to provide investment and business recommendations.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Financial models, market analysis</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
         </is>
       </c>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Treasurer</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>JOB-000018</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Treasurers manage a company's financial assets, including cash flow, investments, and risk management strategies.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Cash management reports, investment plans</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
         </is>
       </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Internal Auditor</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>JOB-000019</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Internal auditors review and evaluate financial and operational processes to ensure compliance, efficiency, and risk mitigation within an organization.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Audit reports, compliance reviews</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
         </is>
       </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Compliance Manager</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>JOB-000020</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Compliance managers develop and enforce policies to ensure an organization adheres to laws, regulations, and internal standards.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Compliance reports, policy guidelines</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
         </is>
       </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Compliance Officer</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>JOB-000021</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Compliance officers monitor and report on organizational adherence to legal standards, ensuring that financial and operational activities meet regulatory requirements.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Compliance audit reports, risk assessments</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
         </is>
       </c>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Real Estate Analyst</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>JOB-000022</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Real estate analysts assess property values, market trends, and investment opportunities, providing data-driven recommendations for investment decisions.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Market analysis reports, property valuations</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
         </is>
       </c>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Risk Analyst</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>JOB-000023</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Risk analysts identify, evaluate, and manage financial and operational risks, using quantitative methods to protect an organization's assets.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Risk models, risk assessments</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
         </is>
       </c>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Administrative Coordinator</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>JOB-000024</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Administrative coordinators manage daily office tasks, including scheduling, correspondence, and organizing meetings and events.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Schedules, event planning, reports</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
         </is>
       </c>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Executive Assistant</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>JOB-000025</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Executive assistants support high-level executives by managing their calendars, arranging meetings, and performing administrative duties.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Calendar schedules, meeting agendas</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
         </is>
       </c>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Office Assistant</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>JOB-000026</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Office assistants handle basic administrative tasks such as answering phones, organizing files, and assisting with office operations.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Filing systems, office organization</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Excel, Word</t>
         </is>
       </c>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Office Head</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>JOB-000027</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>The office head oversees office operations, including managing staff, budgets, and overall office efficiency.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Office management reports, team coordination</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
         </is>
       </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Office Manager</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>JOB-000028</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Office managers supervise office functions, ensure smooth operations, manage supplies, and support administrative teams.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Office systems, inventory management</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
         </is>
       </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Graphic Designer</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>JOB-000029</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Graphic designers create visual content, from logos and websites to marketing materials, ensuring they align with brand identity.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Logos, brochures, websites, advertisements</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
         </is>
       </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Civil Engineer</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>JOB-000030</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Civil engineers design, plan, and oversee construction projects like roads, bridges, and buildings, ensuring safety, functionality, and environmental impact.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Construction blueprints, project plans</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
         </is>
       </c>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Electrical Engineer</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>JOB-000031</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Electrical engineers design and test electrical systems and equipment, ensuring efficiency and safety in applications ranging from consumer electronics to power grids.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Electrical schematics, system designs</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
         </is>
       </c>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Mechanical Engineer</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>JOB-000032</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Mechanical engineers design, analyze, and manufacture mechanical systems, ensuring functionality and durability in industries like automotive and manufacturing.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Product prototypes, mechanical designs</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
         </is>
       </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Process Engineer</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>JOB-000033</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Process engineers design, implement, and optimize industrial processes in manufacturing and production to ensure efficiency, quality, and cost-effectiveness.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Optimized production processes, cost savings</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
         </is>
       </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>JOB-000034</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Team leads supervise and guide team members to meet goals, improve productivity, and foster a collaborative work environment.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Team performance, project results</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
         </is>
       </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Interpreter-Translator</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>JOB-000035</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Interpreters and translators convert spoken or written content from one language to another, ensuring accuracy and cultural sensitivity.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Translated documents, verbal translations</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
         </is>
       </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Language Lead</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>JOB-000036</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Language leads oversee translation projects, manage teams of translators, and ensure quality and accuracy in linguistic services across various languages.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Translated materials, multilingual content</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
         </is>
       </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Facilities Manager</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>JOB-000037</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Facilities managers oversee the day-to-day operations of an organization's physical workspace, ensuring maintenance, safety, and efficiency.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Maintenance schedules, facility reports</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
         </is>
       </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Logistics Coordinator</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>JOB-000038</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Logistics coordinators manage the supply chain, ensuring the timely and cost-effective transportation and storage of goods.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Shipping schedules, inventory reports</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
         </is>
       </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Maintenance Supervisor</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>JOB-000039</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Maintenance supervisors oversee the maintenance and repair of equipment and facilities, ensuring smooth operational flow.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Equipment repair logs, maintenance schedules</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
         </is>
       </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Operations Manager</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>JOB-000040</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Operations managers oversee all aspects of daily business activities, optimizing processes to enhance efficiency, reduce costs, and improve performance.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Operational reports, process optimization</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
         </is>
       </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Plant Manager</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>JOB-000041</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Plant managers oversee manufacturing facilities, ensuring efficient production, safety, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Production schedules, plant safety records</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
         </is>
       </c>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>JOB-000042</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Production supervisors manage the daily activities of production workers, ensuring product quality and on-time completion.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Production output, quality control reports</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Excel, MES software, SAP, Production scheduling tools</t>
         </is>
       </c>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>JOB-000043</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Project managers plan, execute, and close projects, ensuring they are completed on time, within scope, and within budget.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Project plans, timelines, budget reports</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
         </is>
       </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Quality Control Analyst</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>JOB-000044</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Quality control analysts test and inspect products or processes to ensure they meet established standards and regulations.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Quality reports, inspection logs</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
         </is>
       </c>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Lab Technician</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>JOB-000045</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Lab technicians conduct scientific experiments, maintain equipment, and analyze data to assist in research and development projects.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Research findings, test results</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
         </is>
       </c>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Business Planner</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>JOB-000046</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Business planners develop strategic plans that align company goals with market opportunities, analyzing trends and forecasts.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Business plans, market analysis reports</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
         </is>
       </c>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Compensation and Benefits Specialist</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>JOB-000047</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Compensation and benefits specialists manage employee pay, benefits packages, and compensation plans, ensuring compliance and competitiveness.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Compensation reports, benefits strategies</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
         </is>
       </c>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>JOB-000048</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>HR generalists handle various HR functions, including recruitment, employee relations, performance management, and policy implementation.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Employee records, performance reviews</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
         </is>
       </c>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>JOB-000049</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>HR managers oversee HR teams, ensuring the effective management of recruitment, training, employee relations, and performance management.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>HR strategy reports, employee programs</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
         </is>
       </c>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>HR Recruiter</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>JOB-000050</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>HR recruiters source, screen, and hire talent for an organization, managing the recruitment process from job postings to interviews.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Recruitment reports, candidate pipelines</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
         </is>
       </c>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Recruiter</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>JOB-000051</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Recruiters focus on finding and attracting qualified candidates for job openings, guiding them through the hiring process.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Job offers, candidate databases</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
         </is>
       </c>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>JOB-000052</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>HR business partners work closely with business leaders to align HR practices with business goals, focusing on workforce planning, development, and strategy.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>HR strategy reports, talent management plans</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
         </is>
       </c>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Ethics Officer</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>JOB-000053</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Ethics officers develop and enforce ethical guidelines, ensuring compliance with laws and regulations within an organization.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Ethics policies, compliance reports</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
         </is>
       </c>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>AI Programmer</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>JOB-000054</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>AI programmers design and implement artificial intelligence algorithms and systems, creating intelligent solutions for a range of applications.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>AI models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
         </is>
       </c>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>AI Research Scientist</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>JOB-000055</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>AI research scientists conduct advanced research in artificial intelligence, developing new methodologies and pushing the boundaries of machine learning and AI.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Research papers, AI algorithms</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
         </is>
       </c>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Analytics Manager</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>JOB-000056</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Analytics managers oversee data analytics teams, guiding them in deriving actionable insights from large datasets to inform business decisions.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Analytics reports, data insights</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
         </is>
       </c>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Android Developer</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>JOB-000057</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Android developers create mobile applications for Android devices, ensuring seamless user experiences and integration with various device features.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Android apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
         </is>
       </c>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>AR VR Developer</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>JOB-000058</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>AR/VR developers design and implement augmented and virtual reality experiences, creating immersive environments for entertainment, training, and other applications.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>AR/VR apps, immersive experiences</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
         </is>
       </c>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Augmented Reality (AR) Programmer</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>JOB-000059</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>AR programmers develop software that overlays digital content onto the real world, enhancing user interactions through augmented reality technology.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>AR applications, interactive content</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
         </is>
       </c>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Back-End Developer</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>JOB-000060</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Back-end developers focus on server-side programming, building and maintaining the infrastructure that supports web applications and databases.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Web services, APIs, server-side systems</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
         </is>
       </c>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>BI Developer</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>JOB-000061</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Business Intelligence (BI) developers design and implement systems that help organizations analyze and interpret data to improve decision-making.</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>BI dashboards, reporting tools</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
         </is>
       </c>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Big Data Engineer</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>JOB-000062</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Big Data engineers design and manage systems for processing and analyzing large sets of structured and unstructured data across distributed systems.</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Big Data platforms, data pipelines</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
         </is>
       </c>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Blockchain Developer</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>JOB-000063</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Blockchain developers create decentralized applications and blockchain platforms, focusing on secure transactions and data integrity using distributed ledger technology.</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Blockchain apps, decentralized solutions</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
         </is>
       </c>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Business Intelligence Analyst</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>JOB-000064</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>BI analysts evaluate and interpret data to provide insights and recommendations that guide business strategy and improve performance.</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Data reports, business insights</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
         </is>
       </c>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Business Intelligence Developer</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>JOB-000065</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>BI developers design and implement the infrastructure for data analysis, creating dashboards, reports, and other tools for decision-making.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>BI systems, reporting solutions</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
         </is>
       </c>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Business Objects Developer</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>JOB-000066</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Business Objects developers create and manage business intelligence applications, focusing on data integration, reporting, and analytics.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Reports, dashboards, data analysis</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
         </is>
       </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>JOB-000067</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Business analysts assess business processes and identify opportunities for improvement, translating business needs into technical solutions.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Requirements documents, business solutions</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
         </is>
       </c>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Chief Information Officer (CIO)</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>JOB-000068</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>The CIO oversees the IT strategy and operations of an organization, ensuring technology aligns with business goals and drives innovation.</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>IT strategy, technology roadmaps</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
         </is>
       </c>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>JOB-000069</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Cloud engineers design, implement, and maintain cloud-based solutions, ensuring scalability, security, and performance across cloud environments.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Cloud infrastructure, cloud services</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
         </is>
       </c>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Cross-Platform Developer</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>JOB-000070</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Cross-platform developers build applications that run seamlessly on multiple operating systems, reducing development time and cost.</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Multi-platform apps, mobile/web solutions</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
         </is>
       </c>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>JOB-000071</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Cybersecurity analysts protect an organization's systems and data from cyber threats by monitoring for security breaches, vulnerabilities, and attacks.</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
         </is>
       </c>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>JOB-000072</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Data analysts interpret complex data to help organizations make data-driven decisions, often working with raw data and presenting findings to stakeholders.</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Data reports, data visualizations</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
         </is>
       </c>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Data Analytics Consultant</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>JOB-000073</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Data analytics consultants help organizations optimize their data strategy, analyzing business data to provide actionable insights for growth.</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>Analytics reports, recommendations</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
         </is>
       </c>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>Data Architect</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>JOB-000074</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Data architects design and structure data systems, ensuring that data is accessible, secure, and scalable across various platforms and applications.</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Data architecture, data models</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
         </is>
       </c>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Data Center Engineer</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>JOB-000075</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Data center engineers manage and maintain the physical and virtual infrastructure of data centers, ensuring high availability, performance, and security.</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Data center infrastructure, network systems</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
         </is>
       </c>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>JOB-000076</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Data engineers design, build, and maintain data pipelines and infrastructure, ensuring smooth flow and storage of data for analysis.</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>Data pipelines, data storage systems</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
         </is>
       </c>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Data Modeler</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>JOB-000077</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Data modelers design data models, structures, and databases, ensuring that data is stored efficiently and can be easily accessed for analysis.</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Data models, data structures</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
         </is>
       </c>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>JOB-000078</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Data scientists analyze complex data sets using advanced statistical, mathematical, and programming techniques to build models and predictions.</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Predictive models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
         </is>
       </c>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Database Administrator (DBA)</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>JOB-000079</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>DBAs manage and maintain databases, ensuring their performance, integrity, and security while troubleshooting and resolving issues.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Database performance, backups, security</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
         </is>
       </c>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Database Support Specialist</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>JOB-000080</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Database support specialists provide technical support for database systems, troubleshooting issues and ensuring smooth operations.</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Database maintenance, troubleshooting</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
         </is>
       </c>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Database Tester</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>JOB-000081</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Database testers validate and test databases to ensure data accuracy, integrity, and functionality by executing test cases and identifying bugs.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>Test reports, database issues</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
         </is>
       </c>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>Datawarehouse Specialist</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>JOB-000082</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Data warehouse specialists design, implement, and manage large-scale data storage systems, ensuring that data is organized, accessible, and optimized for analysis.</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Data warehouses, ETL pipelines</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
         </is>
       </c>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Deep Learning Specialist</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>JOB-000083</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Deep learning specialists focus on advanced machine learning techniques, creating neural networks and AI models for tasks like image recognition and natural language processing.</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Deep learning models, AI applications</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
         </is>
       </c>
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Desktop Support Technician</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>JOB-000084</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Desktop support technicians troubleshoot and resolve hardware and software issues on desktops and laptops, providing technical support to end users.</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Resolved technical issues, support tickets</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
         </is>
       </c>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="5" t="n"/>
+      <c r="K85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>JOB-000085</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>DevOps engineers automate and streamline the deployment, integration, and monitoring of applications and infrastructure, ensuring faster development cycles.</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Continuous integration pipelines, deployment automation</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
         </is>
       </c>
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="5" t="n"/>
+      <c r="K86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>ETL Developer</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>JOB-000086</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>ETL (Extract, Transform, Load) developers design and manage data workflows to extract data from various sources, transform it into a usable format, and load it into databases.</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>ETL pipelines, data transformations</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
         </is>
       </c>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>Extended Reality (XR) Programmer</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>JOB-000087</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>XR programmers create immersive experiences using augmented reality (AR), virtual reality (VR), and mixed reality (MR), developing applications for various industries.</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>XR applications, immersive experiences</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
         </is>
       </c>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>Front-End Developer</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>JOB-000088</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Front-end developers design and build the user-facing components of websites and applications, ensuring responsive design and user experience.</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Websites, user interfaces, web apps</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
         </is>
       </c>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>Full-Stack Developer</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>JOB-000089</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Full-stack developers handle both the front-end and back-end of web applications, ensuring smooth communication between the user interface and databases.</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Full web applications, APIs, services</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
         </is>
       </c>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Informatica Developer</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>JOB-000090</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Informatica developers design and implement data integration solutions using Informatica tools to facilitate data movement and transformation across platforms.</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>ETL processes, data integrations</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
         </is>
       </c>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>Information Security Analyst</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>JOB-000091</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Information security analysts assess and secure an organization's IT infrastructure by identifying vulnerabilities, monitoring systems, and responding to incidents.</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
         </is>
       </c>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Information Security Officer</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>JOB-000092</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Information security officers develop and enforce policies to protect sensitive data and networks from internal and external threats.</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Security policies, compliance reports</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
         </is>
       </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Infrastructure Architect</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>JOB-000093</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Infrastructure architects design and manage the underlying IT infrastructure, ensuring that systems are scalable, secure, and reliable to support business operations.</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>IT infrastructure, architecture plans</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="5" t="inlineStr">
         <is>
           <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
         </is>
       </c>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="5" t="n"/>
+      <c r="K94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>iOS Developer</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>JOB-000094</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>iOS developers create applications for Apple's ecosystem, ensuring a seamless user experience across iPhones, iPads, and other Apple devices.</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>iOS apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
         </is>
       </c>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>IoT Specialist</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>JOB-000095</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>IoT specialists design and manage interconnected systems and devices, ensuring secure data transfer and real-time functionality for the Internet of Things.</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>IoT solutions, connected devices</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
         </is>
       </c>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>IT Support Specialist</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>JOB-000096</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>IT support specialists provide technical assistance for users, troubleshooting hardware/software issues and maintaining systems and networks.</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>Technical support tickets, system maintenance</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
         </is>
       </c>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+      <c r="K97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>IT Technician</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>JOB-000097</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>IT technicians install, configure, and maintain hardware and software systems, assisting users and ensuring smooth operation of company devices and systems.</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>Hardware setup, software installation</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
         </is>
       </c>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>JOB-000098</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Machine learning engineers develop algorithms that allow systems to improve over time based on data, working with large datasets to build predictive models.</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>Machine learning models, data-driven insights</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
         </is>
       </c>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="n"/>
+      <c r="K99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>MicroStrategy Developer</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>JOB-000099</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>MicroStrategy developers design and implement business intelligence solutions using the MicroStrategy platform, focusing on reporting and data analysis.</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>BI reports, data analytics platforms</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
         </is>
       </c>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="5" t="n"/>
+      <c r="K100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Mixed Reality (MR) Programmer</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>JOB-000100</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>MR programmers develop interactive and immersive experiences using both virtual and augmented reality, blending the real and virtual worlds.</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>MR applications, interactive content</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
         </is>
       </c>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -67,9 +67,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +476,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>industry_id</t>
+          <t>industry_name</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -509,3304 +506,2704 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Product Analyst</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>JOB-000001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Product analysts assess market trends, customer needs, and product performance. They use data to make recommendations for product improvements or new launches.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Product insights, data reports, market analysis</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Outsourcing Manager</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>JOB-000006</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Outsourcing managers are responsible for managing the relationship with external vendors and service providers, ensuring services are delivered on time and within budget.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Vendor contracts, service agreements, cost-saving initiatives</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Excel, SAP, Microsoft Project, Vendor management software</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Procurement Specialist</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>JOB-000007</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Procurement specialists manage the sourcing of materials or services needed by a company, ensuring quality, cost-efficiency, and timely delivery from suppliers.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Supplier contracts, cost-efficient procurement strategies</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Supply Chain Analyst</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>JOB-000008</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Supply chain analysts track and optimize the movement of goods and materials throughout the supply chain, identifying efficiencies and areas for improvement.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Supply chain efficiency, inventory management reports</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>JOB-000009</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Product managers oversee the development and lifecycle of a product, from ideation to launch, ensuring it meets customer needs and business goals.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Product roadmap, feature prioritization, go-to-market strategy</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>JOB-000010</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Product owners work with development teams to ensure that product features and requirements are clearly defined and aligned with business priorities.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Product backlog, feature requirements, sprint planning</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>JIRA, Confluence, Trello, Slack, Aha!</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Franchise Manager</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>JOB-000011</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Franchise managers oversee the operations of franchise locations, ensuring brand standards, profitability, and compliance are maintained across locations.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Franchise operational standards, profitability metrics</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Excel, SAP, POS systems, CRM software</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Corporate Development Manager</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>JOB-000012</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Corporate development managers identify new business opportunities, partnerships, and strategic acquisitions to drive growth and expansion for the company.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Mergers and acquisitions, strategic partnerships</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Strategy Analyst</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>JOB-000013</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Strategy analysts provide insights and recommendations to guide the company's strategic direction, using data and competitive analysis to inform decisions.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Business strategy reports, market trend analysis</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Chief Financial Officer (CFO)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>JOB-000002</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>The CFO oversees the financial operations of an organization, ensuring strategic financial planning, risk management, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Financial strategy, risk management plans</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>R&amp;D Engineer</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>JOB-000003</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>R&amp;D engineers design and develop new products or technologies, conducting experiments and testing prototypes for functionality and feasibility.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Prototypes, technical reports</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>JOB-000004</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Software engineers apply engineering principles to software development, focusing on the development and maintenance of software systems and applications.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Software systems, applications, features</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Game Publisher - Publishing Producer</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>JOB-000005</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Publishing producers manage the relationship between game development teams and publishers, overseeing the release, marketing, and distribution of games.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Game launch, marketing materials, distribution</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Statistician</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>JOB-000014</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Statisticians analyze and interpret data to identify trends and patterns. They design surveys and experiments, and use statistical models to inform decision-making.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Statistical models, reports, insights</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Accountant</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>JOB-000015</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Accountants manage financial records, ensuring accuracy and compliance with regulations. They prepare reports, handle taxes, and assist with budgeting.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Financial statements, tax filings</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>JOB-000016</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Controllers oversee financial operations, ensuring compliance and efficiency. They manage budgeting, forecasting, and financial reporting within an organization.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Budget reports, financial forecasts</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>JOB-000017</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Financial analysts analyze market trends, financial data, and economic conditions to provide investment and business recommendations.</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Financial models, market analysis</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Treasurer</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>JOB-000018</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Treasurers manage a company's financial assets, including cash flow, investments, and risk management strategies.</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Cash management reports, investment plans</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Internal Auditor</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>JOB-000019</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Internal auditors review and evaluate financial and operational processes to ensure compliance, efficiency, and risk mitigation within an organization.</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Audit reports, compliance reviews</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Compliance Manager</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>JOB-000020</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Compliance managers develop and enforce policies to ensure an organization adheres to laws, regulations, and internal standards.</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Compliance reports, policy guidelines</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Compliance Officer</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>JOB-000021</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Compliance officers monitor and report on organizational adherence to legal standards, ensuring that financial and operational activities meet regulatory requirements.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Compliance audit reports, risk assessments</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Real Estate Analyst</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>JOB-000022</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Real estate analysts assess property values, market trends, and investment opportunities, providing data-driven recommendations for investment decisions.</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Market analysis reports, property valuations</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Risk Analyst</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>JOB-000023</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Risk analysts identify, evaluate, and manage financial and operational risks, using quantitative methods to protect an organization's assets.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Risk models, risk assessments</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Administrative Coordinator</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>JOB-000024</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Administrative coordinators manage daily office tasks, including scheduling, correspondence, and organizing meetings and events.</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Schedules, event planning, reports</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Executive Assistant</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>JOB-000025</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Executive assistants support high-level executives by managing their calendars, arranging meetings, and performing administrative duties.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Calendar schedules, meeting agendas</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Office Assistant</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>JOB-000026</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Office assistants handle basic administrative tasks such as answering phones, organizing files, and assisting with office operations.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Filing systems, office organization</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Excel, Word</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Office Head</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>JOB-000027</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>The office head oversees office operations, including managing staff, budgets, and overall office efficiency.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Office management reports, team coordination</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Office Manager</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>JOB-000028</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Office managers supervise office functions, ensure smooth operations, manage supplies, and support administrative teams.</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Office systems, inventory management</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Graphic Designer</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>JOB-000029</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Graphic designers create visual content, from logos and websites to marketing materials, ensuring they align with brand identity.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Logos, brochures, websites, advertisements</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Civil Engineer</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>JOB-000030</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Civil engineers design, plan, and oversee construction projects like roads, bridges, and buildings, ensuring safety, functionality, and environmental impact.</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Construction blueprints, project plans</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Electrical Engineer</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>JOB-000031</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Electrical engineers design and test electrical systems and equipment, ensuring efficiency and safety in applications ranging from consumer electronics to power grids.</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Electrical schematics, system designs</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Mechanical Engineer</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>JOB-000032</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Mechanical engineers design, analyze, and manufacture mechanical systems, ensuring functionality and durability in industries like automotive and manufacturing.</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Product prototypes, mechanical designs</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Process Engineer</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>JOB-000033</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Process engineers design, implement, and optimize industrial processes in manufacturing and production to ensure efficiency, quality, and cost-effectiveness.</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Optimized production processes, cost savings</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>JOB-000034</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Team leads supervise and guide team members to meet goals, improve productivity, and foster a collaborative work environment.</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Team performance, project results</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Interpreter-Translator</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>JOB-000035</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Interpreters and translators convert spoken or written content from one language to another, ensuring accuracy and cultural sensitivity.</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Translated documents, verbal translations</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Language Lead</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>JOB-000036</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Language leads oversee translation projects, manage teams of translators, and ensure quality and accuracy in linguistic services across various languages.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Translated materials, multilingual content</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Facilities Manager</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>JOB-000037</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Facilities managers oversee the day-to-day operations of an organization's physical workspace, ensuring maintenance, safety, and efficiency.</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Maintenance schedules, facility reports</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Logistics Coordinator</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>JOB-000038</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Logistics coordinators manage the supply chain, ensuring the timely and cost-effective transportation and storage of goods.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Shipping schedules, inventory reports</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Maintenance Supervisor</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>JOB-000039</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Maintenance supervisors oversee the maintenance and repair of equipment and facilities, ensuring smooth operational flow.</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Equipment repair logs, maintenance schedules</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Operations Manager</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>JOB-000040</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Operations managers oversee all aspects of daily business activities, optimizing processes to enhance efficiency, reduce costs, and improve performance.</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Operational reports, process optimization</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Plant Manager</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>JOB-000041</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Plant managers oversee manufacturing facilities, ensuring efficient production, safety, and compliance with regulations.</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Production schedules, plant safety records</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>JOB-000042</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Production supervisors manage the daily activities of production workers, ensuring product quality and on-time completion.</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Production output, quality control reports</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Excel, MES software, SAP, Production scheduling tools</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>JOB-000043</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Project managers plan, execute, and close projects, ensuring they are completed on time, within scope, and within budget.</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Project plans, timelines, budget reports</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Quality Control Analyst</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>JOB-000044</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Quality control analysts test and inspect products or processes to ensure they meet established standards and regulations.</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Quality reports, inspection logs</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Lab Technician</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>JOB-000045</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Lab technicians conduct scientific experiments, maintain equipment, and analyze data to assist in research and development projects.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Research findings, test results</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Business Planner</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>JOB-000046</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Business planners develop strategic plans that align company goals with market opportunities, analyzing trends and forecasts.</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Business plans, market analysis reports</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Compensation and Benefits Specialist</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>JOB-000047</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Compensation and benefits specialists manage employee pay, benefits packages, and compensation plans, ensuring compliance and competitiveness.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Compensation reports, benefits strategies</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>HR Generalist</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>JOB-000048</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>HR generalists handle various HR functions, including recruitment, employee relations, performance management, and policy implementation.</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Employee records, performance reviews</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
         </is>
       </c>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>JOB-000049</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>HR managers oversee HR teams, ensuring the effective management of recruitment, training, employee relations, and performance management.</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>HR strategy reports, employee programs</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>HR Recruiter</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>JOB-000050</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>HR recruiters source, screen, and hire talent for an organization, managing the recruitment process from job postings to interviews.</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Recruitment reports, candidate pipelines</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Recruiter</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>JOB-000051</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Recruiters focus on finding and attracting qualified candidates for job openings, guiding them through the hiring process.</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Job offers, candidate databases</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>HR Business Partner</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>JOB-000052</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>HR business partners work closely with business leaders to align HR practices with business goals, focusing on workforce planning, development, and strategy.</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>HR strategy reports, talent management plans</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
         </is>
       </c>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Ethics Officer</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>JOB-000053</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Ethics officers develop and enforce ethical guidelines, ensuring compliance with laws and regulations within an organization.</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Ethics policies, compliance reports</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>AI Programmer</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>JOB-000054</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>AI programmers design and implement artificial intelligence algorithms and systems, creating intelligent solutions for a range of applications.</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>AI models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>AI Research Scientist</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>JOB-000055</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>AI research scientists conduct advanced research in artificial intelligence, developing new methodologies and pushing the boundaries of machine learning and AI.</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Research papers, AI algorithms</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Analytics Manager</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>JOB-000056</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Analytics managers oversee data analytics teams, guiding them in deriving actionable insights from large datasets to inform business decisions.</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Analytics reports, data insights</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Android Developer</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>JOB-000057</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Android developers create mobile applications for Android devices, ensuring seamless user experiences and integration with various device features.</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Android apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>AR VR Developer</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>JOB-000058</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>AR/VR developers design and implement augmented and virtual reality experiences, creating immersive environments for entertainment, training, and other applications.</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>AR/VR apps, immersive experiences</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Augmented Reality (AR) Programmer</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>JOB-000059</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>AR programmers develop software that overlays digital content onto the real world, enhancing user interactions through augmented reality technology.</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>AR applications, interactive content</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Back-End Developer</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>JOB-000060</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Back-end developers focus on server-side programming, building and maintaining the infrastructure that supports web applications and databases.</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Web services, APIs, server-side systems</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>BI Developer</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>JOB-000061</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Business Intelligence (BI) developers design and implement systems that help organizations analyze and interpret data to improve decision-making.</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>BI dashboards, reporting tools</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Big Data Engineer</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>JOB-000062</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Big Data engineers design and manage systems for processing and analyzing large sets of structured and unstructured data across distributed systems.</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Big Data platforms, data pipelines</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Blockchain Developer</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>JOB-000063</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Blockchain developers create decentralized applications and blockchain platforms, focusing on secure transactions and data integrity using distributed ledger technology.</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Blockchain apps, decentralized solutions</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Business Intelligence Analyst</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>JOB-000064</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>BI analysts evaluate and interpret data to provide insights and recommendations that guide business strategy and improve performance.</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Data reports, business insights</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Business Intelligence Developer</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>JOB-000065</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>BI developers design and implement the infrastructure for data analysis, creating dashboards, reports, and other tools for decision-making.</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>BI systems, reporting solutions</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Business Objects Developer</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>JOB-000066</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Business Objects developers create and manage business intelligence applications, focusing on data integration, reporting, and analytics.</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Reports, dashboards, data analysis</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>JOB-000067</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Business analysts assess business processes and identify opportunities for improvement, translating business needs into technical solutions.</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Requirements documents, business solutions</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Chief Information Officer (CIO)</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>JOB-000068</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>The CIO oversees the IT strategy and operations of an organization, ensuring technology aligns with business goals and drives innovation.</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>IT strategy, technology roadmaps</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>JOB-000069</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Cloud engineers design, implement, and maintain cloud-based solutions, ensuring scalability, security, and performance across cloud environments.</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Cloud infrastructure, cloud services</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Cross-Platform Developer</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>JOB-000070</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Cross-platform developers build applications that run seamlessly on multiple operating systems, reducing development time and cost.</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Multi-platform apps, mobile/web solutions</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Cybersecurity Analyst</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>JOB-000071</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Cybersecurity analysts protect an organization's systems and data from cyber threats by monitoring for security breaches, vulnerabilities, and attacks.</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>JOB-000072</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Data analysts interpret complex data to help organizations make data-driven decisions, often working with raw data and presenting findings to stakeholders.</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Data reports, data visualizations</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Data Analytics Consultant</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>JOB-000073</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Data analytics consultants help organizations optimize their data strategy, analyzing business data to provide actionable insights for growth.</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Analytics reports, recommendations</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Data Architect</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>JOB-000074</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Data architects design and structure data systems, ensuring that data is accessible, secure, and scalable across various platforms and applications.</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Data architecture, data models</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Data Center Engineer</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>JOB-000075</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Data center engineers manage and maintain the physical and virtual infrastructure of data centers, ensuring high availability, performance, and security.</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Data center infrastructure, network systems</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>JOB-000076</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Data engineers design, build, and maintain data pipelines and infrastructure, ensuring smooth flow and storage of data for analysis.</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Data pipelines, data storage systems</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Data Modeler</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>JOB-000077</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Data modelers design data models, structures, and databases, ensuring that data is stored efficiently and can be easily accessed for analysis.</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Data models, data structures</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>JOB-000078</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Data scientists analyze complex data sets using advanced statistical, mathematical, and programming techniques to build models and predictions.</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Predictive models, machine learning algorithms</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Database Administrator (DBA)</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>JOB-000079</t>
         </is>
       </c>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>DBAs manage and maintain databases, ensuring their performance, integrity, and security while troubleshooting and resolving issues.</t>
         </is>
       </c>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Database performance, backups, security</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Database Support Specialist</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>JOB-000080</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Database support specialists provide technical support for database systems, troubleshooting issues and ensuring smooth operations.</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Database maintenance, troubleshooting</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Database Tester</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>JOB-000081</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Database testers validate and test databases to ensure data accuracy, integrity, and functionality by executing test cases and identifying bugs.</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Test reports, database issues</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Datawarehouse Specialist</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>JOB-000082</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Data warehouse specialists design, implement, and manage large-scale data storage systems, ensuring that data is organized, accessible, and optimized for analysis.</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n"/>
-      <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Data warehouses, ETL pipelines</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Deep Learning Specialist</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>JOB-000083</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Deep learning specialists focus on advanced machine learning techniques, creating neural networks and AI models for tasks like image recognition and natural language processing.</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Deep learning models, AI applications</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Desktop Support Technician</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>JOB-000084</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Desktop support technicians troubleshoot and resolve hardware and software issues on desktops and laptops, providing technical support to end users.</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Resolved technical issues, support tickets</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>DevOps Engineer</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>JOB-000085</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>DevOps engineers automate and streamline the deployment, integration, and monitoring of applications and infrastructure, ensuring faster development cycles.</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n"/>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Continuous integration pipelines, deployment automation</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>ETL Developer</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>JOB-000086</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>ETL (Extract, Transform, Load) developers design and manage data workflows to extract data from various sources, transform it into a usable format, and load it into databases.</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n"/>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>ETL pipelines, data transformations</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Extended Reality (XR) Programmer</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>JOB-000087</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>XR programmers create immersive experiences using augmented reality (AR), virtual reality (VR), and mixed reality (MR), developing applications for various industries.</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>XR applications, immersive experiences</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Front-End Developer</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>JOB-000088</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Front-end developers design and build the user-facing components of websites and applications, ensuring responsive design and user experience.</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Websites, user interfaces, web apps</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Full-Stack Developer</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>JOB-000089</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Full-stack developers handle both the front-end and back-end of web applications, ensuring smooth communication between the user interface and databases.</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Full web applications, APIs, services</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Informatica Developer</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>JOB-000090</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Informatica developers design and implement data integration solutions using Informatica tools to facilitate data movement and transformation across platforms.</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>ETL processes, data integrations</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Information Security Analyst</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>JOB-000091</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Information security analysts assess and secure an organization's IT infrastructure by identifying vulnerabilities, monitoring systems, and responding to incidents.</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Security protocols, vulnerability reports</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Information Security Officer</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>JOB-000092</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Information security officers develop and enforce policies to protect sensitive data and networks from internal and external threats.</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Security policies, compliance reports</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Infrastructure Architect</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>JOB-000093</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Infrastructure architects design and manage the underlying IT infrastructure, ensuring that systems are scalable, secure, and reliable to support business operations.</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>IT infrastructure, architecture plans</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>iOS Developer</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>JOB-000094</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>iOS developers create applications for Apple's ecosystem, ensuring a seamless user experience across iPhones, iPads, and other Apple devices.</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>iOS apps, mobile solutions</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>IoT Specialist</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>JOB-000095</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>IoT specialists design and manage interconnected systems and devices, ensuring secure data transfer and real-time functionality for the Internet of Things.</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>IoT solutions, connected devices</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>IT Support Specialist</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>JOB-000096</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>IT support specialists provide technical assistance for users, troubleshooting hardware/software issues and maintaining systems and networks.</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Technical support tickets, system maintenance</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>IT Technician</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>JOB-000097</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>IT technicians install, configure, and maintain hardware and software systems, assisting users and ensuring smooth operation of company devices and systems.</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Hardware setup, software installation</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
         </is>
       </c>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Machine Learning Engineer</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>JOB-000098</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Machine learning engineers develop algorithms that allow systems to improve over time based on data, working with large datasets to build predictive models.</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n"/>
-      <c r="F99" s="5" t="n"/>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Machine learning models, data-driven insights</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
         </is>
       </c>
-      <c r="I99" s="5" t="n"/>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>MicroStrategy Developer</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>JOB-000099</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>MicroStrategy developers design and implement business intelligence solutions using the MicroStrategy platform, focusing on reporting and data analysis.</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>BI reports, data analytics platforms</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
         </is>
       </c>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Mixed Reality (MR) Programmer</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>JOB-000100</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>MR programmers develop interactive and immersive experiences using both virtual and augmented reality, blending the real and virtual worlds.</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>MR applications, interactive content</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
         </is>
       </c>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/jobs.xlsx
+++ b/apps/api/data/excel_templates/jobs.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Product insights, data reports, market analysis</t>
+          <t>Product insights;data reports;market analysis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Excel, SQL, Tableau, Google Analytics, Python, JIRA</t>
+          <t>Excel;SQL;Tableau;Google Analytics;Python;JIRA</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vendor contracts, service agreements, cost-saving initiatives</t>
+          <t>Vendor contracts;service agreements;cost-saving initiatives</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Excel, SAP, Microsoft Project, Vendor management software</t>
+          <t>Excel;SAP;Microsoft Project;Vendor management software</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Supplier contracts, cost-efficient procurement strategies</t>
+          <t>Supplier contracts;cost-efficient procurement strategies</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SAP, Oracle Procurement, Excel, Purchase Order Software</t>
+          <t>SAP;Oracle Procurement;Excel;Purchase Order Software</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Supply chain efficiency, inventory management reports</t>
+          <t>Supply chain efficiency;inventory management reports</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Excel, SAP, Oracle, Tableau, Python, Lean/Six Sigma</t>
+          <t>Excel;SAP;Oracle;Tableau;Python;Lean/Six Sigma</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Product roadmap, feature prioritization, go-to-market strategy</t>
+          <t>Product roadmap;feature prioritization;go-to-market strategy</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>JIRA, Trello, Productboard, Google Analytics, SQL</t>
+          <t>JIRA;Trello;Productboard;Google Analytics;SQL</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Product backlog, feature requirements, sprint planning</t>
+          <t>Product backlog;feature requirements;sprint planning</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>JIRA, Confluence, Trello, Slack, Aha!</t>
+          <t>JIRA;Confluence;Trello;Slack;Aha!</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Franchise operational standards, profitability metrics</t>
+          <t>Franchise operational standards;profitability metrics</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Excel, SAP, POS systems, CRM software</t>
+          <t>Excel;SAP;POS systems;CRM software</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mergers and acquisitions, strategic partnerships</t>
+          <t>Mergers and acquisitions;strategic partnerships</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Microsoft Excel, Salesforce, PowerPoint, CRM systems</t>
+          <t>Microsoft Excel;Salesforce;PowerPoint;CRM systems</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Business strategy reports, market trend analysis</t>
+          <t>Business strategy reports;market trend analysis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Excel, Tableau, Google Analytics, SQL, PowerPoint</t>
+          <t>Excel;Tableau;Google Analytics;SQL;PowerPoint</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Financial strategy, risk management plans</t>
+          <t>Financial strategy;risk management plans</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SAP, Excel, Oracle, Tableau, Financial Modeling tools, ERP systems</t>
+          <t>SAP;Excel;Oracle;Tableau;Financial Modeling tools;ERP systems</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prototypes, technical reports</t>
+          <t>Prototypes;technical reports</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SolidWorks, MATLAB, Python, LabVIEW, AutoCAD, 3D printers</t>
+          <t>SolidWorks;MATLAB;Python;LabVIEW;AutoCAD;3D printers</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Software systems, applications, features</t>
+          <t>Software systems;applications;features</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C++, Java, Python, Git, Docker, Kubernetes, Agile methodologies</t>
+          <t>C++;Java;Python;Git;Docker;Kubernetes;Agile methodologies</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Game launch, marketing materials, distribution</t>
+          <t>Game launch;marketing materials;distribution</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jira, Trello, Slack, Excel, MS Office, Digital distribution platforms (Steam, Epic Games)</t>
+          <t>Jira;Trello;Slack;Excel;MS Office;Digital distribution platforms (Steam;Epic Games)</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Statistical models, reports, insights</t>
+          <t>Statistical models;reports;insights</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R, Python, SAS, SPSS, Excel, MATLAB, SQL</t>
+          <t>R;Python;SAS;SPSS;Excel;MATLAB;SQL</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Financial statements, tax filings</t>
+          <t>Financial statements;tax filings</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>QuickBooks, Xero, Excel, SAP, Oracle, FreshBooks</t>
+          <t>QuickBooks;Xero;Excel;SAP;Oracle;FreshBooks</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Budget reports, financial forecasts</t>
+          <t>Budget reports;financial forecasts</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SAP, Excel, Oracle, Hyperion, Adaptive Insights</t>
+          <t>SAP;Excel;Oracle;Hyperion;Adaptive Insights</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Financial models, market analysis</t>
+          <t>Financial models;market analysis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Excel, Bloomberg Terminal, Python, Tableau, Power BI</t>
+          <t>Excel;Bloomberg Terminal;Python;Tableau;Power BI</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cash management reports, investment plans</t>
+          <t>Cash management reports;investment plans</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SAP, Excel, Treasury Management Systems, Bloomberg Terminal, Python</t>
+          <t>SAP;Excel;Treasury Management Systems;Bloomberg Terminal;Python</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Audit reports, compliance reviews</t>
+          <t>Audit reports;compliance reviews</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SAP, Oracle, ACL, TeamMate, Microsoft Office</t>
+          <t>SAP;Oracle;ACL;TeamMate;Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Compliance reports, policy guidelines</t>
+          <t>Compliance reports;policy guidelines</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Compliance software, SAP, SharePoint, Excel, LexisNexis</t>
+          <t>Compliance software;SAP;SharePoint;Excel;LexisNexis</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Compliance audit reports, risk assessments</t>
+          <t>Compliance audit reports;risk assessments</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Compliance software, Excel, SAP, GRC platforms (e.g., MetricStream, LogicGate)</t>
+          <t>Compliance software;Excel;SAP;GRC platforms (e.g.;MetricStream;LogicGate)</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Market analysis reports, property valuations</t>
+          <t>Market analysis reports;property valuations</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Argus, Excel, CoStar, REFM, GIS software, Tableau</t>
+          <t>Argus;Excel;CoStar;REFM;GIS software;Tableau</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Risk models, risk assessments</t>
+          <t>Risk models;risk assessments</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Excel, MATLAB, Python, R, Bloomberg Terminal, Risk Management software</t>
+          <t>Excel;MATLAB;Python;R;Bloomberg Terminal;Risk Management software</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Schedules, event planning, reports</t>
+          <t>Schedules;event planning;reports</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Microsoft Office, Google Workspace, Trello, Asana, Zoom</t>
+          <t>Microsoft Office;Google Workspace;Trello;Asana;Zoom</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calendar schedules, meeting agendas</t>
+          <t>Calendar schedules;meeting agendas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Microsoft Office, Google Calendar, Zoom, Slack, Concur</t>
+          <t>Microsoft Office;Google Calendar;Zoom;Slack;Concur</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Filing systems, office organization</t>
+          <t>Filing systems;office organization</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Microsoft Office, Google Workspace, Excel, Word</t>
+          <t>Microsoft Office;Google Workspace;Excel;Word</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Office management reports, team coordination</t>
+          <t>Office management reports;team coordination</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Microsoft Office, Google Workspace, Project management tools (Asana, Trello)</t>
+          <t>Microsoft Office;Google Workspace;Project management tools (Asana;Trello)</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Office systems, inventory management</t>
+          <t>Office systems;inventory management</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Microsoft Office, Google Workspace, QuickBooks, Office management software</t>
+          <t>Microsoft Office;Google Workspace;QuickBooks;Office management software</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Logos, brochures, websites, advertisements</t>
+          <t>Logos;brochures;websites;advertisements</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Adobe Creative Suite (Photoshop, Illustrator, InDesign), Figma, Sketch, Canva</t>
+          <t>Adobe Creative Suite (Photoshop;Illustrator;InDesign);Figma;Sketch;Canva</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Construction blueprints, project plans</t>
+          <t>Construction blueprints;project plans</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AutoCAD, Revit, Civil 3D, GIS software, SAP2000, ETABS</t>
+          <t>AutoCAD;Revit;Civil 3D;GIS software;SAP2000;ETABS</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Electrical schematics, system designs</t>
+          <t>Electrical schematics;system designs</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AutoCAD Electrical, MATLAB, Simulink, PLC software, LabVIEW, PSpice</t>
+          <t>AutoCAD Electrical;MATLAB;Simulink;PLC software;LabVIEW;PSpice</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Product prototypes, mechanical designs</t>
+          <t>Product prototypes;mechanical designs</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SolidWorks, AutoCAD, MATLAB, CATIA, ANSYS, FEA software</t>
+          <t>SolidWorks;AutoCAD;MATLAB;CATIA;ANSYS;FEA software</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Optimized production processes, cost savings</t>
+          <t>Optimized production processes;cost savings</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AutoCAD, MATLAB, Process Simulation Software, Aspen Plus, PLCs</t>
+          <t>AutoCAD;MATLAB;Process Simulation Software;Aspen Plus;PLCs</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Team performance, project results</t>
+          <t>Team performance;project results</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Slack, Microsoft Teams, Asana, Trello, Zoom, Google Workspace</t>
+          <t>Slack;Microsoft Teams;Asana;Trello;Zoom;Google Workspace</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Translated documents, verbal translations</t>
+          <t>Translated documents;verbal translations</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CAT tools (SDL Trados, MemoQ), Word, Google Translate, Speech-to-text software</t>
+          <t>CAT tools (SDL Trados;MemoQ);Word;Google Translate;Speech-to-text software</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Translated materials, multilingual content</t>
+          <t>Translated materials;multilingual content</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CAT tools, Project management software (Trello, Asana), Word, Excel</t>
+          <t>CAT tools;Project management software (Trello;Asana);Word;Excel</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Maintenance schedules, facility reports</t>
+          <t>Maintenance schedules;facility reports</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CMMS (Computerized Maintenance Management Systems), Microsoft Office, AutoCAD</t>
+          <t>CMMS (Computerized Maintenance Management Systems);Microsoft Office;AutoCAD</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Shipping schedules, inventory reports</t>
+          <t>Shipping schedules;inventory reports</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SAP, Excel, Oracle, logistics management software (Transporeon, FourKites)</t>
+          <t>SAP;Excel;Oracle;logistics management software (Transporeon;FourKites)</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Equipment repair logs, maintenance schedules</t>
+          <t>Equipment repair logs;maintenance schedules</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CMMS, Excel, AutoCAD, PLCs, inventory management systems</t>
+          <t>CMMS;Excel;AutoCAD;PLCs;inventory management systems</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Operational reports, process optimization</t>
+          <t>Operational reports;process optimization</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Microsoft Office, SAP, Oracle, ERP systems, Lean management tools</t>
+          <t>Microsoft Office;SAP;Oracle;ERP systems;Lean management tools</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Production schedules, plant safety records</t>
+          <t>Production schedules;plant safety records</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ERP software (SAP, Oracle), AutoCAD, CMMS, Lean Six Sigma tools</t>
+          <t>ERP software (SAP;Oracle);AutoCAD;CMMS;Lean Six Sigma tools</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Production output, quality control reports</t>
+          <t>Production output;quality control reports</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Excel, MES software, SAP, Production scheduling tools</t>
+          <t>Excel;MES software;SAP;Production scheduling tools</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Project plans, timelines, budget reports</t>
+          <t>Project plans;timelines;budget reports</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MS Project, Trello, Asana, Jira, Slack, Microsoft Office</t>
+          <t>MS Project;Trello;Asana;Jira;Slack;Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Quality reports, inspection logs</t>
+          <t>Quality reports;inspection logs</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Excel, Minitab, Statistical Process Control (SPC) software, CAD software</t>
+          <t>Excel;Minitab;Statistical Process Control (SPC) software;CAD software</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Research findings, test results</t>
+          <t>Research findings;test results</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lab equipment, MATLAB, Python, Excel, PCR machines, microscopes</t>
+          <t>Lab equipment;MATLAB;Python;Excel;PCR machines;microscopes</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Business plans, market analysis reports</t>
+          <t>Business plans;market analysis reports</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Microsoft Office, Power BI, Tableau, Excel, strategic planning tools</t>
+          <t>Microsoft Office;Power BI;Tableau;Excel;strategic planning tools</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Compensation reports, benefits strategies</t>
+          <t>Compensation reports;benefits strategies</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SAP, Workday, ADP, Excel, PayScale, PeopleSoft</t>
+          <t>SAP;Workday;ADP;Excel;PayScale;PeopleSoft</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Employee records, performance reviews</t>
+          <t>Employee records;performance reviews</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Workday, SAP SuccessFactors, BambooHR, ADP, Microsoft Office</t>
+          <t>Workday;SAP SuccessFactors;BambooHR;ADP;Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HR strategy reports, employee programs</t>
+          <t>HR strategy reports;employee programs</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Workday, SAP, PeopleSoft, HRIS systems, Microsoft Office</t>
+          <t>Workday;SAP;PeopleSoft;HRIS systems;Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Recruitment reports, candidate pipelines</t>
+          <t>Recruitment reports;candidate pipelines</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>LinkedIn Recruiter, Workday, BambooHR, ATS systems (Greenhouse, Lever)</t>
+          <t>LinkedIn Recruiter;Workday;BambooHR;ATS systems (Greenhouse;Lever)</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Job offers, candidate databases</t>
+          <t>Job offers;candidate databases</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>LinkedIn, Indeed, ATS software, Microsoft Office, Zoom</t>
+          <t>LinkedIn;Indeed;ATS software;Microsoft Office;Zoom</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HR strategy reports, talent management plans</t>
+          <t>HR strategy reports;talent management plans</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors, Workday, Excel, Power BI</t>
+          <t>SAP SuccessFactors;Workday;Excel;Power BI</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ethics policies, compliance reports</t>
+          <t>Ethics policies;compliance reports</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Legal software, Microsoft Office, Compliance management systems (GRC)</t>
+          <t>Legal software;Microsoft Office;Compliance management systems (GRC)</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>AI models, machine learning algorithms</t>
+          <t>AI models;machine learning algorithms</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Python, TensorFlow, PyTorch, Keras, Jupyter Notebooks, AWS</t>
+          <t>Python;TensorFlow;PyTorch;Keras;Jupyter Notebooks;AWS</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Research papers, AI algorithms</t>
+          <t>Research papers;AI algorithms</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Python, TensorFlow, PyTorch, MATLAB, Jupyter Notebooks, GPU computing</t>
+          <t>Python;TensorFlow;PyTorch;MATLAB;Jupyter Notebooks;GPU computing</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Analytics reports, data insights</t>
+          <t>Analytics reports;data insights</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SQL, Tableau, Power BI, Python, R, Hadoop, Google Analytics, Excel</t>
+          <t>SQL;Tableau;Power BI;Python;R;Hadoop;Google Analytics;Excel</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Android apps, mobile solutions</t>
+          <t>Android apps;mobile solutions</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Java, Kotlin, Android Studio, Firebase, REST APIs, Git</t>
+          <t>Java;Kotlin;Android Studio;Firebase;REST APIs;Git</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AR/VR apps, immersive experiences</t>
+          <t>AR/VR apps;immersive experiences</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Unity, Unreal Engine, C#, ARCore, ARKit, VR hardware (HTC Vive, Oculus Rift)</t>
+          <t>Unity;Unreal Engine;C#;ARCore;ARKit;VR hardware (HTC Vive;Oculus Rift)</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AR applications, interactive content</t>
+          <t>AR applications;interactive content</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Unity, ARCore, ARKit, Vuforia, C#, OpenCV</t>
+          <t>Unity;ARCore;ARKit;Vuforia;C#;OpenCV</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Web services, APIs, server-side systems</t>
+          <t>Web services;APIs;server-side systems</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Java, Python, Ruby, Node.js, SQL, MongoDB, RESTful APIs, Docker</t>
+          <t>Java;Python;Ruby;Node.js;SQL;MongoDB;RESTful APIs;Docker</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BI dashboards, reporting tools</t>
+          <t>BI dashboards;reporting tools</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SQL, Power BI, Tableau, SSRS, ETL tools, DAX, Python</t>
+          <t>SQL;Power BI;Tableau;SSRS;ETL tools;DAX;Python</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Big Data platforms, data pipelines</t>
+          <t>Big Data platforms;data pipelines</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hadoop, Spark, Hive, NoSQL databases, Kafka, Python, Scala</t>
+          <t>Hadoop;Spark;Hive;NoSQL databases;Kafka;Python;Scala</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Blockchain apps, decentralized solutions</t>
+          <t>Blockchain apps;decentralized solutions</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ethereum, Solidity, Node.js, Hyperledger, Truffle, Web3.js</t>
+          <t>Ethereum;Solidity;Node.js;Hyperledger;Truffle;Web3.js</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Data reports, business insights</t>
+          <t>Data reports;business insights</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Excel, Power BI, Tableau, SQL, Google Analytics, R</t>
+          <t>Excel;Power BI;Tableau;SQL;Google Analytics;R</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BI systems, reporting solutions</t>
+          <t>BI systems;reporting solutions</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SQL, Power BI, Tableau, SSRS, ETL tools, SQL Server, DAX</t>
+          <t>SQL;Power BI;Tableau;SSRS;ETL tools;SQL Server;DAX</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Reports, dashboards, data analysis</t>
+          <t>Reports;dashboards;data analysis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SAP BusinessObjects, Crystal Reports, SQL, Web Intelligence</t>
+          <t>SAP BusinessObjects;Crystal Reports;SQL;Web Intelligence</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Requirements documents, business solutions</t>
+          <t>Requirements documents;business solutions</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SQL, Excel, Jira, Microsoft Office, BPM tools</t>
+          <t>SQL;Excel;Jira;Microsoft Office;BPM tools</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IT strategy, technology roadmaps</t>
+          <t>IT strategy;technology roadmaps</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ERP systems, IT governance tools, cloud solutions, project management tools</t>
+          <t>ERP systems;IT governance tools;cloud solutions;project management tools</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cloud infrastructure, cloud services</t>
+          <t>Cloud infrastructure;cloud services</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud, Terraform, Kubernetes, Docker, Python, Linux</t>
+          <t>AWS;Azure;Google Cloud;Terraform;Kubernetes;Docker;Python;Linux</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Multi-platform apps, mobile/web solutions</t>
+          <t>Multi-platform apps;mobile/web solutions</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>React Native, Flutter, Xamarin, JavaScript, Java, Dart</t>
+          <t>React Native;Flutter;Xamarin;JavaScript;Java;Dart</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Security protocols, vulnerability reports</t>
+          <t>Security protocols;vulnerability reports</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Firewalls, SIEM, VPNs, IDS/IPS, Wireshark, Kali Linux, Python</t>
+          <t>Firewalls;SIEM;VPNs;IDS/IPS;Wireshark;Kali Linux;Python</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Data reports, data visualizations</t>
+          <t>Data reports;data visualizations</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Excel, SQL, Tableau, Power BI, R, Python, Google Analytics</t>
+          <t>Excel;SQL;Tableau;Power BI;R;Python;Google Analytics</t>
         </is>
       </c>
     </row>
@@ -2467,12 +2467,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Analytics reports, recommendations</t>
+          <t>Analytics reports;recommendations</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SQL, R, Python, Power BI, Tableau, SAS, Hadoop, Excel</t>
+          <t>SQL;R;Python;Power BI;Tableau;SAS;Hadoop;Excel</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Data architecture, data models</t>
+          <t>Data architecture;data models</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SQL, NoSQL, Hadoop, Spark, AWS, Google Cloud, MongoDB, Erwin Data Modeler</t>
+          <t>SQL;NoSQL;Hadoop;Spark;AWS;Google Cloud;MongoDB;Erwin Data Modeler</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Data center infrastructure, network systems</t>
+          <t>Data center infrastructure;network systems</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Server hardware, virtualization tools (VMware, Hyper-V), Linux, Python, SNMP</t>
+          <t>Server hardware;virtualization tools (VMware;Hyper-V);Linux;Python;SNMP</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Data pipelines, data storage systems</t>
+          <t>Data pipelines;data storage systems</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SQL, Python, Hadoop, Spark, Kafka, ETL tools, AWS, Azure</t>
+          <t>SQL;Python;Hadoop;Spark;Kafka;ETL tools;AWS;Azure</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Data models, data structures</t>
+          <t>Data models;data structures</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Erwin, IBM InfoSphere, SQL, NoSQL, UML, PowerDesigner</t>
+          <t>Erwin;IBM InfoSphere;SQL;NoSQL;UML;PowerDesigner</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Predictive models, machine learning algorithms</t>
+          <t>Predictive models;machine learning algorithms</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Python, R, TensorFlow, Hadoop, Spark, SQL, Jupyter Notebooks</t>
+          <t>Python;R;TensorFlow;Hadoop;Spark;SQL;Jupyter Notebooks</t>
         </is>
       </c>
     </row>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Database performance, backups, security</t>
+          <t>Database performance;backups;security</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SQL, Oracle, MySQL, MongoDB, DB2, T-SQL, PostgreSQL, Backup tools</t>
+          <t>SQL;Oracle;MySQL;MongoDB;DB2;T-SQL;PostgreSQL;Backup tools</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Database maintenance, troubleshooting</t>
+          <t>Database maintenance;troubleshooting</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SQL, Oracle, MySQL, PostgreSQL, T-SQL, DB2</t>
+          <t>SQL;Oracle;MySQL;PostgreSQL;T-SQL;DB2</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Test reports, database issues</t>
+          <t>Test reports;database issues</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SQL, Selenium, JMeter, TestComplete, DB2, Oracle</t>
+          <t>SQL;Selenium;JMeter;TestComplete;DB2;Oracle</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Data warehouses, ETL pipelines</t>
+          <t>Data warehouses;ETL pipelines</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SQL, Oracle, Hadoop, AWS Redshift, Microsoft SQL Server, Informatica, Talend</t>
+          <t>SQL;Oracle;Hadoop;AWS Redshift;Microsoft SQL Server;Informatica;Talend</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Deep learning models, AI applications</t>
+          <t>Deep learning models;AI applications</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, Python, CUDA, Jupyter Notebooks</t>
+          <t>TensorFlow;PyTorch;Keras;Python;CUDA;Jupyter Notebooks</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Resolved technical issues, support tickets</t>
+          <t>Resolved technical issues;support tickets</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Windows OS, Mac OS, Active Directory, ServiceNow, Remote Desktop tools, TeamViewer</t>
+          <t>Windows OS;Mac OS;Active Directory;ServiceNow;Remote Desktop tools;TeamViewer</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Continuous integration pipelines, deployment automation</t>
+          <t>Continuous integration pipelines;deployment automation</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Jenkins, Docker, Kubernetes, Git, Terraform, AWS, Azure, Ansible, Chef, Puppet</t>
+          <t>Jenkins;Docker;Kubernetes;Git;Terraform;AWS;Azure;Ansible;Chef;Puppet</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ETL pipelines, data transformations</t>
+          <t>ETL pipelines;data transformations</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SQL, Informatica, Talend, Microsoft SSIS, Apache Nifi, Python, DataStage</t>
+          <t>SQL;Informatica;Talend;Microsoft SSIS;Apache Nifi;Python;DataStage</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>XR applications, immersive experiences</t>
+          <t>XR applications;immersive experiences</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Unity, Unreal Engine, C#, XR SDKs (ARCore, ARKit, Vuforia), OpenCV, Oculus SDK</t>
+          <t>Unity;Unreal Engine;C#;XR SDKs (ARCore;ARKit;Vuforia);OpenCV;Oculus SDK</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Websites, user interfaces, web apps</t>
+          <t>Websites;user interfaces;web apps</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HTML, CSS, JavaScript, React, Angular, Vue.js, Bootstrap, Sass, jQuery</t>
+          <t>HTML;CSS;JavaScript;React;Angular;Vue.js;Bootstrap;Sass;jQuery</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Full web applications, APIs, services</t>
+          <t>Full web applications;APIs;services</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>HTML, CSS, JavaScript, Node.js, React, Angular, MongoDB, SQL, Docker, Git</t>
+          <t>HTML;CSS;JavaScript;Node.js;React;Angular;MongoDB;SQL;Docker;Git</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ETL processes, data integrations</t>
+          <t>ETL processes;data integrations</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Informatica PowerCenter, SQL, Data Warehousing tools, Unix, Shell scripting</t>
+          <t>Informatica PowerCenter;SQL;Data Warehousing tools;Unix;Shell scripting</t>
         </is>
       </c>
     </row>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Security protocols, vulnerability reports</t>
+          <t>Security protocols;vulnerability reports</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>SIEM tools, Firewalls, VPNs, IDS/IPS, Splunk, Wireshark, Nessus, Kali Linux</t>
+          <t>SIEM tools;Firewalls;VPNs;IDS/IPS;Splunk;Wireshark;Nessus;Kali Linux</t>
         </is>
       </c>
     </row>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Security policies, compliance reports</t>
+          <t>Security policies;compliance reports</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>SIEM tools, firewalls, endpoint security, encryption tools, compliance software</t>
+          <t>SIEM tools;firewalls;endpoint security;encryption tools;compliance software</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT infrastructure, architecture plans</t>
+          <t>IT infrastructure;architecture plans</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>VMware, AWS, Azure, Cisco, Terraform, Ansible, Linux, Windows Server</t>
+          <t>VMware;AWS;Azure;Cisco;Terraform;Ansible;Linux;Windows Server</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>iOS apps, mobile solutions</t>
+          <t>iOS apps;mobile solutions</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Swift, Xcode, Objective-C, Cocoa Touch, Firebase, RESTful APIs, Git</t>
+          <t>Swift;Xcode;Objective-C;Cocoa Touch;Firebase;RESTful APIs;Git</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IoT solutions, connected devices</t>
+          <t>IoT solutions;connected devices</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Arduino, Raspberry Pi, MQTT, Zigbee, Bluetooth, Python, IoT frameworks</t>
+          <t>Arduino;Raspberry Pi;MQTT;Zigbee;Bluetooth;Python;IoT frameworks</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Technical support tickets, system maintenance</t>
+          <t>Technical support tickets;system maintenance</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Windows OS, macOS, Active Directory, Helpdesk software, Remote Desktop tools</t>
+          <t>Windows OS;macOS;Active Directory;Helpdesk software;Remote Desktop tools</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hardware setup, software installation</t>
+          <t>Hardware setup;software installation</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Windows OS, macOS, Network configuration tools, Antivirus software, ServiceNow</t>
+          <t>Windows OS;macOS;Network configuration tools;Antivirus software;ServiceNow</t>
         </is>
       </c>
     </row>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Machine learning models, data-driven insights</t>
+          <t>Machine learning models;data-driven insights</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Python, R, TensorFlow, PyTorch, Scikit-learn, Keras, Jupyter Notebooks, Hadoop</t>
+          <t>Python;R;TensorFlow;PyTorch;Scikit-learn;Keras;Jupyter Notebooks;Hadoop</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BI reports, data analytics platforms</t>
+          <t>BI reports;data analytics platforms</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>MicroStrategy, SQL, Tableau, Oracle, Power BI, Excel, DAX</t>
+          <t>MicroStrategy;SQL;Tableau;Oracle;Power BI;Excel;DAX</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MR applications, interactive content</t>
+          <t>MR applications;interactive content</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Unity, Unreal Engine, C#, MR SDKs, HoloLens, ARKit, ARCore, OpenXR</t>
+          <t>Unity;Unreal Engine;C#;MR SDKs;HoloLens;ARKit;ARCore;OpenXR</t>
         </is>
       </c>
     </row>
